--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -714,11 +714,11 @@
       <c r="C8" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0</v>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>3</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>4</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>2</v>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="15">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.8243243243243243</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>748</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>28 mục (SL-01..SL-28)</t>
+          <t>30 mục (SL-01..SL-30)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2830,8 +2830,98 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C60" s="20" t="inlineStr">
+        <is>
+          <t>Biên dịch từng module rồi liên kết riêng</t>
+        </is>
+      </c>
+      <c r="D60" s="20" t="inlineStr">
+        <is>
+          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
+        </is>
+      </c>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>TC-40 (19 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C61" s="20" t="inlineStr">
+        <is>
+          <t>Ráp ảnh nạp được (.elf → .hex)</t>
+        </is>
+      </c>
+      <c r="D61" s="20" t="inlineStr">
+        <is>
+          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
+        </is>
+      </c>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py</t>
+        </is>
+      </c>
+      <c r="F61" s="20" t="inlineStr">
+        <is>
+          <t>TC-40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C62" s="20" t="inlineStr">
+        <is>
+          <t>Đo kích thước nói rõ đang đo tầm nào</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>TC-40d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F59"/>
+  <autoFilter ref="A1:F62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2842,7 +2932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2921,17 +3011,17 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Biên dịch từng module rồi link riêng</t>
+          <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>Lệnh compile của pack hiện có -o nên luôn link, mà link thì đòi main()</t>
+          <t>Chuỗi dịch → liên kết → ảnh nạp được đã có; còn thiếu chính main() và bộ định thời</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
@@ -2941,7 +3031,7 @@
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Sửa lệnh compile thành -c, thêm năng lực link riêng. ĐÂY LÀ MẮT XÍCH CHẶN ĐẦU TIÊN: chưa có nó thì không có tệp .hex để nạp</t>
+          <t>Cần mẫu main() + bộ định thời hợp tác gọi các module đã merge (bước 2 của lộ trình)</t>
         </is>
       </c>
     </row>
@@ -3071,17 +3161,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>D. Sinh mã</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Hiện sinh được từng module rời, chưa ráp thành một chương trình chạy được</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3091,7 +3181,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Cần mẫu main() + bộ định thời hợp tác, và một cổng kiểm 'ráp xong có build không'</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3101,17 +3191,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Liệt kê cổng serial, đoán mạch nào đang cắm</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3121,7 +3211,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Cần bộ liệt kê cổng theo hệ điều hành; là mắt xích đầu của nhóm J</t>
         </is>
       </c>
     </row>
@@ -3131,17 +3221,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Liệt kê cổng serial, đoán mạch nào đang cắm</t>
+          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -3151,7 +3241,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Cần bộ liệt kê cổng theo hệ điều hành; là mắt xích đầu của nhóm J</t>
+          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3256,12 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -3181,7 +3271,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3286,12 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -3211,7 +3301,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3221,17 +3311,17 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -3241,7 +3331,7 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3346,12 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán từ mẫu</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -3271,7 +3361,7 @@
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3281,62 +3371,32 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F16"/>
+  <autoFilter ref="A1:F15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3401,17 +3461,17 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 ✔</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Tách biên dịch và liên kết</t>
+          <t>Tách biên dịch và liên kết — XONG</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>Sửa năng lực compile của pack thành -c cho từng module; thêm năng lực link gộp các .o + main() thành .elf; thêm năng lực hex đổi .elf sang .hex</t>
+          <t>compile dùng -c cho từng tệp nguồn; link gộp tệp đối tượng + main() thành .elf; hex đổi sang định dạng nạp được. TC-40, 19 test</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -3421,7 +3481,7 @@
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>packs/avr/pack.yaml, eaa/tools/compile.py</t>
+          <t>packs/avr/pack.yaml, eaa/tools/compile.py, eaa/platform.py</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$62</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -709,13 +709,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" s="8" t="n">
         <v>3</v>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>8</v>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.8243243243243243</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>772</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30 mục (SL-01..SL-30)</t>
+          <t>31 mục (SL-01..SL-31)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1906,27 +1906,27 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>Bốn cổng công cụ</t>
+          <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>compile, static, unittests, size — mỗi cổng trả ToolReport có bằng chứng</t>
+          <t>Sinh vòng lặp chính từ khuôn của pack, dịch mọi module đã merge, liên kết, ra ảnh nạp được</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/</t>
+          <t>eaa/firmware.py + eaa build</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>TC-07 (43 test)</t>
+          <t>TC-41 (24 test)</t>
         </is>
       </c>
     </row>
@@ -1936,27 +1936,27 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>Bất biến merge</t>
+          <t>Bộ định thời hợp tác</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Chỉ merge khi TOÀN BỘ ToolReport.passed VÀ G3 duyệt; không có nhánh thứ hai</t>
+          <t>Bảng việc định kỳ; ngắt chỉ tăng bộ đếm, đọc bộ đếm trong khối nguyên tử</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>eaa/vcs.py + orchestrator</t>
+          <t>packs/avr/templates/main.c.tmpl</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>TC-01 (45 test)</t>
+          <t>TC-41</t>
         </is>
       </c>
     </row>
@@ -1966,27 +1966,27 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>Băm nội dung xuyên suốt</t>
+          <t>Module đã merge không được bỏ quên khi ráp</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>Hồ sơ gate → quyết định → ủy quyền merge cùng một băm: người duyệt X thì merge đúng X</t>
+          <t>Merge mà vắng mặt trong firmware.yaml là LỖI; không chạy định kỳ thì khai step: null</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py, eaa/vcs.py</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-41b</t>
         </is>
       </c>
     </row>
@@ -1996,27 +1996,27 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>5 Human Gate không vượt được</t>
+          <t>Mã chưa merge không vào được firmware</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Không có cờ --yes / --force / --skip-gate nào tồn tại trong CLI</t>
+          <t>Bản thiết kế ráp nhắc tới module chưa qua G3 thì dừng</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>TC-01, TC-28, TC-34</t>
+          <t>TC-41c</t>
         </is>
       </c>
     </row>
@@ -2031,22 +2031,22 @@
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Phiên không có người ≠ người đồng ý</t>
+          <t>Bốn cổng công cụ</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>Không phải TTY thì ném GateNotInteractive chứ không mặc định duyệt</t>
+          <t>compile, static, unittests, size — mỗi cổng trả ToolReport có bằng chứng</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/tools/</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>TC-28</t>
+          <t>TC-07 (43 test)</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2061,22 @@
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình không đi vào vòng tự sửa</t>
+          <t>Bất biến merge</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Thiếu luật, thiếu công cụ → chặn ngay, không đốt 3 lượt sửa vô ích</t>
+          <t>Chỉ merge khi TOÀN BỘ ToolReport.passed VÀ G3 duyệt; không có nhánh thứ hai</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>eaa/orchestrator.py</t>
+          <t>eaa/vcs.py + orchestrator</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-01 (45 test)</t>
         </is>
       </c>
     </row>
@@ -2091,22 +2091,22 @@
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>Sổ lỗi ảo giác</t>
+          <t>Băm nội dung xuyên suốt</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>Append-only; phân xử ghi thành sự kiện mới chứ không sửa sự kiện cũ</t>
+          <t>Hồ sơ gate → quyết định → ủy quyền merge cùng một băm: người duyệt X thì merge đúng X</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>eaa/ledger.py</t>
+          <t>eaa/gates.py, eaa/vcs.py</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>TC-10 (20 test)</t>
+          <t>TC-01</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2121,22 @@
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>Báo cáo KPI</t>
+          <t>5 Human Gate không vượt được</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Tỉ lệ qua cổng, số lượt tự sửa, token tiêu thụ theo module</t>
+          <t>Không có cờ --yes / --force / --skip-gate nào tồn tại trong CLI</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>eaa/kpi.py + eaa report</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>TC-09</t>
+          <t>TC-01, TC-28, TC-34</t>
         </is>
       </c>
     </row>
@@ -2146,27 +2146,27 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>F. Mô phỏng</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>Mô hình con lắc ngược + MIL</t>
+          <t>Phiên không có người ≠ người đồng ý</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Mô phỏng động lực học, đánh giá theo tiêu chí nghiệm thu</t>
+          <t>Không phải TTY thì ném GateNotInteractive chứ không mặc định duyệt</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/sim.py, sim_runner.py</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>TC-12 (12 test)</t>
+          <t>TC-28</t>
         </is>
       </c>
     </row>
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>F. Mô phỏng</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>Quét tham số</t>
+          <t>Lỗi cấu hình không đi vào vòng tự sửa</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Quét lưới bộ tham số điều khiển, xếp hạng theo chỉ số</t>
+          <t>Thiếu luật, thiếu công cụ → chặn ngay, không đốt 3 lượt sửa vô ích</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>eaa sim --sweep</t>
+          <t>eaa/orchestrator.py</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>TC-12</t>
+          <t>TC-06</t>
         </is>
       </c>
     </row>
@@ -2206,27 +2206,27 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>F. Mô phỏng</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>Chỉ số thời gian ổn định đo đúng</t>
+          <t>Sổ lỗi ảo giác</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Đo từ lần cuối tín hiệu rời dải, tính từ lúc nhiễu kết thúc</t>
+          <t>Append-only; phân xử ghi thành sự kiện mới chứ không sửa sự kiện cũ</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/sim.py</t>
+          <t>eaa/ledger.py</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>test_sim_verification.py</t>
+          <t>TC-10 (20 test)</t>
         </is>
       </c>
     </row>
@@ -2236,27 +2236,27 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>Chế độ 1 — quét công cụ đã có</t>
+          <t>Báo cáo KPI</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Có gì trên máy, phiên bản bao nhiêu, thiếu thì chặn cổng nào</t>
+          <t>Tỉ lệ qua cổng, số lượt tự sửa, token tiêu thụ theo module</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>eaa doctor</t>
+          <t>eaa/kpi.py + eaa report</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>TC-34 (37 test)</t>
+          <t>TC-09</t>
         </is>
       </c>
     </row>
@@ -2266,27 +2266,27 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>F. Mô phỏng</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>Chế độ 2 — sinh lệnh cài</t>
+          <t>Mô hình con lắc ngược + MIL</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Sinh đúng lệnh theo hệ điều hành, hỏi người trước từng lệnh</t>
+          <t>Mô phỏng động lực học, đánh giá theo tiêu chí nghiệm thu</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>eaa doctor --fix</t>
+          <t>eaa/tools/sim.py, sim_runner.py</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>TC-34, TC-37</t>
+          <t>TC-12 (12 test)</t>
         </is>
       </c>
     </row>
@@ -2296,27 +2296,27 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>F. Mô phỏng</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>Chế độ 3 — TỰ TÌM công cụ chưa biết</t>
+          <t>Quét tham số</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Phát hiện → tra cứu bằng mô hình → đề xuất; đây là phần vừa làm xong</t>
+          <t>Quét lưới bộ tham số điều khiển, xếp hạng theo chỉ số</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>eaa/toolsearch.py</t>
+          <t>eaa sim --sweep</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>TC-39 (29 test)</t>
+          <t>TC-12</t>
         </is>
       </c>
     </row>
@@ -2326,27 +2326,27 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>F. Mô phỏng</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>Nhu cầu công cụ suy từ Platform Pack</t>
+          <t>Chỉ số thời gian ổn định đo đúng</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>Không chép tay danh sách: pack.yaml đã ghi mọi chương trình nó gọi</t>
+          <t>Đo từ lần cuối tín hiệu rời dải, tính từ lúc nhiễu kết thúc</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>eaa/toolsearch.py</t>
+          <t>eaa/tools/sim.py</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>TC-39</t>
+          <t>test_sim_verification.py</t>
         </is>
       </c>
     </row>
@@ -2361,22 +2361,22 @@
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>Kiểm nguồn cài trước khi tới tay người</t>
+          <t>Chế độ 1 — quét công cụ đã có</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>10 trình quản lý gói chính thống; tải trực tiếp phải HTTPS + miền cho phép + sha256</t>
+          <t>Có gì trên máy, phiên bản bao nhiêu, thiếu thì chặn cổng nào</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>eaa/toolsearch.py</t>
+          <t>eaa doctor</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>TC-39</t>
+          <t>TC-34 (37 test)</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2391,22 @@
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>Đề xuất công cụ vào manifest qua G2</t>
+          <t>Chế độ 2 — sinh lệnh cài</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Append + supersede, mang theo approved_by / approved_at</t>
+          <t>Sinh đúng lệnh theo hệ điều hành, hỏi người trước từng lệnh</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>eaa gate approve G2</t>
+          <t>eaa doctor --fix</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>TC-39</t>
+          <t>TC-34, TC-37</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>Ràng buộc phiên bản của pack đè lên đề xuất</t>
+          <t>Chế độ 3 — TỰ TÌM công cụ chưa biết</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>pack.yaml ghi avr-gcc &gt;=12.0, mô hình đề xuất 7.3 — lấy theo pack</t>
+          <t>Phát hiện → tra cứu bằng mô hình → đề xuất; đây là phần vừa làm xong</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>TC-39</t>
+          <t>TC-39 (29 test)</t>
         </is>
       </c>
     </row>
@@ -2451,22 +2451,22 @@
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>Khóa môi trường + cảnh báo trôi</t>
+          <t>Nhu cầu công cụ suy từ Platform Pack</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>env_lock.json; toolchain đổi phiên bản thì cảnh báo trước khi so sánh A/B</t>
+          <t>Không chép tay danh sách: pack.yaml đã ghi mọi chương trình nó gọi</t>
         </is>
       </c>
       <c r="E47" s="20" t="inlineStr">
         <is>
-          <t>eaa/doctor.py</t>
+          <t>eaa/toolsearch.py</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>TC-36</t>
+          <t>TC-39</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2481,22 @@
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>Thẻ công cụ</t>
+          <t>Kiểm nguồn cài trước khi tới tay người</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Cú pháp gọi, cách đọc dòng lỗi, phiên bản đã xác nhận</t>
+          <t>10 trình quản lý gói chính thống; tải trực tiếp phải HTTPS + miền cho phép + sha256</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>eaa/doctor.py</t>
+          <t>eaa/toolsearch.py</t>
         </is>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
-          <t>TC-37</t>
+          <t>TC-39</t>
         </is>
       </c>
     </row>
@@ -2506,27 +2506,27 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>Ba hạng chất lượng</t>
+          <t>Đề xuất công cụ vào manifest qua G2</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
+          <t>Append + supersede, mang theo approved_by / approved_at</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>eaa/versions.py</t>
+          <t>eaa gate approve G2</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
         <is>
-          <t>TC-30 (26 test)</t>
+          <t>TC-39</t>
         </is>
       </c>
     </row>
@@ -2536,27 +2536,27 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>known_good.lock chỉ cập nhật tại G4</t>
+          <t>Ràng buộc phiên bản của pack đè lên đề xuất</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
+          <t>pack.yaml ghi avr-gcc &gt;=12.0, mô hình đề xuất 7.3 — lấy theo pack</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>eaa/versions.py</t>
+          <t>eaa/toolsearch.py</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-39</t>
         </is>
       </c>
     </row>
@@ -2566,27 +2566,27 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>Quay lui về bản known-good</t>
+          <t>Khóa môi trường + cảnh báo trôi</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>Rollback không làm mất bản known-good đang giữ</t>
+          <t>env_lock.json; toolchain đổi phiên bản thì cảnh báo trước khi so sánh A/B</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
         <is>
-          <t>eaa rollback</t>
+          <t>eaa/doctor.py</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-36</t>
         </is>
       </c>
     </row>
@@ -2596,27 +2596,27 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>Commit truy vết đầy đủ (NFR-07)</t>
+          <t>Thẻ công cụ</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
+          <t>Cú pháp gọi, cách đọc dòng lỗi, phiên bản đã xác nhận</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>eaa/vcs.py</t>
+          <t>eaa/doctor.py</t>
         </is>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-37</t>
         </is>
       </c>
     </row>
@@ -2631,22 +2631,22 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>Kho phẩm xuất</t>
+          <t>Ba hạng chất lượng</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
+          <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>eaa docs</t>
+          <t>eaa/versions.py</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>TC-32 (33 test)</t>
+          <t>TC-30 (26 test)</t>
         </is>
       </c>
     </row>
@@ -2656,27 +2656,27 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>17 lệnh CLI phủ 10 use case</t>
+          <t>known_good.lock chỉ cập nhật tại G4</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
+          <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>eaa/cli.py</t>
+          <t>eaa/versions.py</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>test_cli_e2e.py</t>
+          <t>TC-30</t>
         </is>
       </c>
     </row>
@@ -2686,27 +2686,27 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>Hồ sơ gate đủ để quyết định</t>
+          <t>Quay lui về bản known-good</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
+          <t>Rollback không làm mất bản known-good đang giữ</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa rollback</t>
         </is>
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>TC-01, TC-28</t>
+          <t>TC-30</t>
         </is>
       </c>
     </row>
@@ -2716,27 +2716,27 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>Từ chối phải có lý do</t>
+          <t>Commit truy vết đầy đủ (NFR-07)</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
+          <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/vcs.py</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
         <is>
-          <t>TC-28</t>
+          <t>TC-01</t>
         </is>
       </c>
     </row>
@@ -2746,27 +2746,27 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Kho phẩm xuất</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
+          <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa docs</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>TC-27 (33 test)</t>
+          <t>TC-32 (33 test)</t>
         </is>
       </c>
     </row>
@@ -2776,27 +2776,27 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
+          <t>17 lệnh CLI phủ 10 use case</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
+          <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>projects/*/diagnostics.yaml</t>
+          <t>eaa/cli.py</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
-          <t>TC-27</t>
+          <t>test_cli_e2e.py</t>
         </is>
       </c>
     </row>
@@ -2806,27 +2806,27 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
+          <t>Hồ sơ gate đủ để quyết định</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
+          <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>TC-27</t>
+          <t>TC-01, TC-28</t>
         </is>
       </c>
     </row>
@@ -2836,27 +2836,27 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>Biên dịch từng module rồi liên kết riêng</t>
+          <t>Từ chối phải có lý do</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
+          <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>TC-40 (19 test)</t>
+          <t>TC-28</t>
         </is>
       </c>
     </row>
@@ -2871,22 +2871,22 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>Ráp ảnh nạp được (.elf → .hex)</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
+          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>TC-40c</t>
+          <t>TC-27 (33 test)</t>
         </is>
       </c>
     </row>
@@ -2901,27 +2901,177 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
+          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
+        </is>
+      </c>
+      <c r="D62" s="20" t="inlineStr">
+        <is>
+          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
+        </is>
+      </c>
+      <c r="E62" s="20" t="inlineStr">
+        <is>
+          <t>projects/*/diagnostics.yaml</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C63" s="20" t="inlineStr">
+        <is>
+          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
+        </is>
+      </c>
+      <c r="D63" s="20" t="inlineStr">
+        <is>
+          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
+        </is>
+      </c>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>eaa/diagnostics.py</t>
+        </is>
+      </c>
+      <c r="F63" s="20" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>Biên dịch từng module rồi liên kết riêng</t>
+        </is>
+      </c>
+      <c r="D64" s="20" t="inlineStr">
+        <is>
+          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>TC-40 (19 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C65" s="20" t="inlineStr">
+        <is>
+          <t>Ráp ảnh nạp được (.elf → .hex)</t>
+        </is>
+      </c>
+      <c r="D65" s="20" t="inlineStr">
+        <is>
+          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
+        </is>
+      </c>
+      <c r="E65" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py</t>
+        </is>
+      </c>
+      <c r="F65" s="20" t="inlineStr">
+        <is>
+          <t>TC-40c</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C66" s="20" t="inlineStr">
+        <is>
           <t>Đo kích thước nói rõ đang đo tầm nào</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D66" s="20" t="inlineStr">
         <is>
           <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
         </is>
       </c>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="E66" s="20" t="inlineStr">
         <is>
           <t>eaa/tools/compile.py</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F66" s="20" t="inlineStr">
         <is>
           <t>TC-40d</t>
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C67" s="20" t="inlineStr">
+        <is>
+          <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>TC-41e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F62"/>
+  <autoFilter ref="A1:F67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2932,7 +3082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3011,17 +3161,17 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>D. Sinh mã</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
+          <t>Nạp firmware xuống mạch qua USB</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>Chuỗi dịch → liên kết → ảnh nạp được đã có; còn thiếu chính main() và bộ định thời</t>
+          <t>avrdude đã vào manifest và biết cách cài, nhưng chưa nối vào lệnh CLI nào</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
@@ -3031,7 +3181,7 @@
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Cần mẫu main() + bộ định thời hợp tác gọi các module đã merge (bước 2 của lộ trình)</t>
+          <t>Cần lệnh 'eaa flash' gọi năng lực flash của pack, kèm G4-style xác nhận người</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3196,12 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Nạp firmware xuống mạch qua USB</t>
+          <t>Đọc telemetry UART thật</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>avrdude đã vào manifest và biết cách cài, nhưng chưa nối vào lệnh CLI nào</t>
+          <t>Hiện --telemetry đọc từ TỆP, không đọc từ cổng nối tiếp</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
@@ -3061,7 +3211,7 @@
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Cần lệnh 'eaa flash' gọi năng lực flash của pack, kèm G4-style xác nhận người</t>
+          <t>Cần bộ đọc serial (pyserial), khung tin có checksum + nhãn thời gian, và hạn thời gian chờ để không treo phiên</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3226,12 @@
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>Đọc telemetry UART thật</t>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Hiện --telemetry đọc từ TỆP, không đọc từ cổng nối tiếp</t>
+          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -3091,7 +3241,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Cần bộ đọc serial (pyserial), khung tin có checksum + nhãn thời gian, và hạn thời gian chờ để không treo phiên</t>
+          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
         </is>
       </c>
     </row>
@@ -3101,27 +3251,27 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+          <t>Tầng 2 của AIS §4.2</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
+          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
         </is>
       </c>
     </row>
@@ -3131,17 +3281,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Tầng 2 của AIS §4.2</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3151,7 +3301,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3161,17 +3311,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Liệt kê cổng serial, đoán mạch nào đang cắm</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3181,7 +3331,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Cần bộ liệt kê cổng theo hệ điều hành; là mắt xích đầu của nhóm J</t>
         </is>
       </c>
     </row>
@@ -3191,17 +3341,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Liệt kê cổng serial, đoán mạch nào đang cắm</t>
+          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3211,7 +3361,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Cần bộ liệt kê cổng theo hệ điều hành; là mắt xích đầu của nhóm J</t>
+          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3376,12 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -3241,7 +3391,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3406,12 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -3271,7 +3421,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3281,17 +3431,17 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -3301,7 +3451,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
         </is>
       </c>
     </row>
@@ -3316,12 +3466,12 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán từ mẫu</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -3331,7 +3481,7 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3341,62 +3491,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F15"/>
+  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3488,17 +3608,17 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2 ✔</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Ráp firmware hoàn chỉnh</t>
+          <t>Ráp firmware hoàn chỉnh — XONG</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Mẫu main() + bộ định thời hợp tác gọi lần lượt các module đã merge; một cổng kiểm 'ráp xong có build sạch không'</t>
+          <t>Khuôn vòng lặp chính ở pack (bộ định thời hợp tác); firmware.yaml khai module nào chạy mỗi bao nhiêu ms; `eaa build` dịch, liên kết, ra .hex. TC-41</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -3508,7 +3628,7 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>packs/avr/templates/, eaa/orchestrator.py</t>
+          <t>packs/avr/templates/, eaa/firmware.py, eaa/cli.py</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -787,19 +787,19 @@
         <v>11</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>1</v>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>2</v>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8765432098765432</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>799</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>31 mục (SL-01..SL-31)</t>
+          <t>33 mục (SL-01..SL-33)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2626,27 +2626,27 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>Ba hạng chất lượng</t>
+          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
+          <t>Liệt kê cổng nối tiếp, khớp VID/PID với bo dự án khai; không đọc được thì nói thẳng</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>eaa/versions.py</t>
+          <t>eaa/serialport.py + eaa ports</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>TC-30 (26 test)</t>
+          <t>TC-42a (8 test)</t>
         </is>
       </c>
     </row>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>known_good.lock chỉ cập nhật tại G4</t>
+          <t>Ba hạng chất lượng</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
+          <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-30 (26 test)</t>
         </is>
       </c>
     </row>
@@ -2691,17 +2691,17 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>Quay lui về bản known-good</t>
+          <t>known_good.lock chỉ cập nhật tại G4</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>Rollback không làm mất bản known-good đang giữ</t>
+          <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
         <is>
-          <t>eaa rollback</t>
+          <t>eaa/versions.py</t>
         </is>
       </c>
       <c r="F55" s="20" t="inlineStr">
@@ -2721,22 +2721,22 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>Commit truy vết đầy đủ (NFR-07)</t>
+          <t>Quay lui về bản known-good</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
+          <t>Rollback không làm mất bản known-good đang giữ</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>eaa/vcs.py</t>
+          <t>eaa rollback</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-30</t>
         </is>
       </c>
     </row>
@@ -2751,22 +2751,22 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>Kho phẩm xuất</t>
+          <t>Commit truy vết đầy đủ (NFR-07)</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
+          <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>eaa docs</t>
+          <t>eaa/vcs.py</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>TC-32 (33 test)</t>
+          <t>TC-01</t>
         </is>
       </c>
     </row>
@@ -2776,27 +2776,27 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>17 lệnh CLI phủ 10 use case</t>
+          <t>Kho phẩm xuất</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
+          <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>eaa/cli.py</t>
+          <t>eaa docs</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
-          <t>test_cli_e2e.py</t>
+          <t>TC-32 (33 test)</t>
         </is>
       </c>
     </row>
@@ -2811,22 +2811,22 @@
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>Hồ sơ gate đủ để quyết định</t>
+          <t>17 lệnh CLI phủ 10 use case</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
+          <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/cli.py</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>TC-01, TC-28</t>
+          <t>test_cli_e2e.py</t>
         </is>
       </c>
     </row>
@@ -2841,12 +2841,12 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>Từ chối phải có lý do</t>
+          <t>Hồ sơ gate đủ để quyết định</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
+          <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>TC-28</t>
+          <t>TC-01, TC-28</t>
         </is>
       </c>
     </row>
@@ -2866,27 +2866,27 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Từ chối phải có lý do</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
+          <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>TC-27 (33 test)</t>
+          <t>TC-28</t>
         </is>
       </c>
     </row>
@@ -2901,22 +2901,22 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
+          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>projects/*/diagnostics.yaml</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>TC-27</t>
+          <t>TC-27 (33 test)</t>
         </is>
       </c>
     </row>
@@ -2931,17 +2931,17 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
+          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
+          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>projects/*/diagnostics.yaml</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
@@ -2961,22 +2961,22 @@
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>Biên dịch từng module rồi liên kết riêng</t>
+          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
+          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>TC-40 (19 test)</t>
+          <t>TC-27</t>
         </is>
       </c>
     </row>
@@ -2991,22 +2991,22 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>Ráp ảnh nạp được (.elf → .hex)</t>
+          <t>Biên dịch từng module rồi liên kết riêng</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
+          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py</t>
+          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>TC-40c</t>
+          <t>TC-40 (19 test)</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>Đo kích thước nói rõ đang đo tầm nào</t>
+          <t>Ráp ảnh nạp được (.elf → .hex)</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
+          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>TC-40d</t>
+          <t>TC-40c</t>
         </is>
       </c>
     </row>
@@ -3051,27 +3051,177 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
+          <t>Đo kích thước nói rõ đang đo tầm nào</t>
+        </is>
+      </c>
+      <c r="D67" s="20" t="inlineStr">
+        <is>
+          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
+        </is>
+      </c>
+      <c r="E67" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/compile.py</t>
+        </is>
+      </c>
+      <c r="F67" s="20" t="inlineStr">
+        <is>
+          <t>TC-40d</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C68" s="20" t="inlineStr">
+        <is>
           <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D68" s="20" t="inlineStr">
         <is>
           <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E68" s="20" t="inlineStr">
         <is>
           <t>eaa/firmware.py</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F68" s="20" t="inlineStr">
         <is>
           <t>TC-41e</t>
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C69" s="20" t="inlineStr">
+        <is>
+          <t>Nạp firmware xuống mạch qua USB</t>
+        </is>
+      </c>
+      <c r="D69" s="20" t="inlineStr">
+        <is>
+          <t>eaa flash gọi năng lực flash của pack; bốn phép kiểm rồi mới hỏi người</t>
+        </is>
+      </c>
+      <c r="E69" s="20" t="inlineStr">
+        <is>
+          <t>eaa/flash.py + eaa flash</t>
+        </is>
+      </c>
+      <c r="F69" s="20" t="inlineStr">
+        <is>
+          <t>TC-42 (30 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C70" s="20" t="inlineStr">
+        <is>
+          <t>Bốn phép kiểm trước khi nạp</t>
+        </is>
+      </c>
+      <c r="D70" s="20" t="inlineStr">
+        <is>
+          <t>Có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận — đều là 'không', không phải cảnh báo</t>
+        </is>
+      </c>
+      <c r="E70" s="20" t="inlineStr">
+        <is>
+          <t>eaa/flash.py</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>TC-42b, TC-42c</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C71" s="20" t="inlineStr">
+        <is>
+          <t>Nhật ký nạp append-only</t>
+        </is>
+      </c>
+      <c r="D71" s="20" t="inlineStr">
+        <is>
+          <t>Commit nào, ảnh nào (kèm băm), cổng nào, ai, lúc nào — ghi cả lần trượt</t>
+        </is>
+      </c>
+      <c r="E71" s="20" t="inlineStr">
+        <is>
+          <t>eaa flash --history</t>
+        </is>
+      </c>
+      <c r="F71" s="20" t="inlineStr">
+        <is>
+          <t>TC-42d</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="inlineStr">
+        <is>
+          <t>Engine không đoán cổng để nạp</t>
+        </is>
+      </c>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>Nhận ra đúng một cổng thì tự chọn; mơ hồ thì dừng và đòi --port</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>eaa/cli.py</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>TC-42e</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F67"/>
+  <autoFilter ref="A1:F72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3082,7 +3232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3166,12 +3316,12 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Nạp firmware xuống mạch qua USB</t>
+          <t>Đọc telemetry UART thật</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>avrdude đã vào manifest và biết cách cài, nhưng chưa nối vào lệnh CLI nào</t>
+          <t>Hiện --telemetry đọc từ TỆP, không đọc từ cổng nối tiếp</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
@@ -3181,7 +3331,7 @@
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Cần lệnh 'eaa flash' gọi năng lực flash của pack, kèm G4-style xác nhận người</t>
+          <t>Cần bộ đọc serial (pyserial), khung tin có checksum + nhãn thời gian, và hạn thời gian chờ để không treo phiên</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3346,12 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Đọc telemetry UART thật</t>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Hiện --telemetry đọc từ TỆP, không đọc từ cổng nối tiếp</t>
+          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
@@ -3211,7 +3361,7 @@
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Cần bộ đọc serial (pyserial), khung tin có checksum + nhãn thời gian, và hạn thời gian chờ để không treo phiên</t>
+          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
         </is>
       </c>
     </row>
@@ -3221,27 +3371,27 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+          <t>Tầng 2 của AIS §4.2</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
+          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
         </is>
       </c>
     </row>
@@ -3251,17 +3401,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Tầng 2 của AIS §4.2</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -3271,7 +3421,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3281,17 +3431,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3301,7 +3451,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
         </is>
       </c>
     </row>
@@ -3311,17 +3461,17 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Liệt kê cổng serial, đoán mạch nào đang cắm</t>
+          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3331,7 +3481,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Cần bộ liệt kê cổng theo hệ điều hành; là mắt xích đầu của nhóm J</t>
+          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3496,12 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3361,7 +3511,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3521,17 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -3391,7 +3541,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
         </is>
       </c>
     </row>
@@ -3401,17 +3551,17 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -3421,7 +3571,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3431,92 +3581,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán từ mẫu</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
-        </is>
-      </c>
-      <c r="E12" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3635,17 +3725,17 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3 ✔</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>Liệt kê cổng USB</t>
+          <t>Liệt kê cổng USB — XONG</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Liệt kê cổng nối tiếp theo hệ điều hành, đoán mạch đang cắm qua VID/PID</t>
+          <t>eaa ports; khớp VID/PID với bo khai ở hardware_profile.yaml; thiếu pyserial thì nói thẳng là không đọc được VID/PID. TC-42a</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -3655,24 +3745,24 @@
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>eaa/serialport.py (mới)</t>
+          <t>eaa/serialport.py</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 ✔</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Lệnh nạp firmware</t>
+          <t>Lệnh nạp firmware — XONG</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>eaa flash gọi năng lực flash của pack; xác nhận người BẮT BUỘC theo FR-DIA-02; ghi lại đã nạp bản commit nào lên thiết bị nào lúc nào</t>
+          <t>eaa flash: bốn phép kiểm (có ảnh · kho sạch · ảnh mới hơn nguồn · người xác nhận) rồi mới nạp; nhật ký append-only ghi cả lần trượt. TC-42</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -3682,7 +3772,7 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>eaa/cli.py, eaa/diagnostics.py</t>
+          <t>eaa/flash.py, eaa/cli.py</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$72</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>2</v>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="15">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>7</v>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.8765432098765432</v>
+        <v>0.8928571428571429</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>827</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33 mục (SL-01..SL-33)</t>
+          <t>34 mục (SL-01..SL-34)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3220,8 +3220,128 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="inlineStr">
+        <is>
+          <t>Đọc telemetry UART thật</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>eaa telemetry thu thẳng từ cổng; diagnose run --port dùng luôn kênh máy sống</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>eaa/telemetry.py</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>TC-43 (28 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C74" s="20" t="inlineStr">
+        <is>
+          <t>Khung telemetry có checksum</t>
+        </is>
+      </c>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>Định dạng khung do dự án khai; mỗi loại hỏng có lý do riêng</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>eaa/telemetry.py</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>TC-43a</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="20" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C75" s="20" t="inlineStr">
+        <is>
+          <t>Phiên thu nhiều khung hỏng bị từ chối</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>Vượt ngưỡng thì không kết luận: dữ liệu nhiễu vẫn cho ra số trông hợp lý</t>
+        </is>
+      </c>
+      <c r="E75" s="20" t="inlineStr">
+        <is>
+          <t>eaa/telemetry.py</t>
+        </is>
+      </c>
+      <c r="F75" s="20" t="inlineStr">
+        <is>
+          <t>TC-43c</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C76" s="20" t="inlineStr">
+        <is>
+          <t>Giữ nguyên văn bản thu, phát lại được</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>Bản thô cạnh bản đã lọc; phân tích lại không cần mạch</t>
+        </is>
+      </c>
+      <c r="E76" s="20" t="inlineStr">
+        <is>
+          <t>eaa telemetry --replay</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>TC-43d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F72"/>
+  <autoFilter ref="A1:F76"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3232,7 +3352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3316,12 +3436,12 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Đọc telemetry UART thật</t>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>Hiện --telemetry đọc từ TỆP, không đọc từ cổng nối tiếp</t>
+          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
@@ -3331,7 +3451,7 @@
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Cần bộ đọc serial (pyserial), khung tin có checksum + nhãn thời gian, và hạn thời gian chờ để không treo phiên</t>
+          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
         </is>
       </c>
     </row>
@@ -3341,27 +3461,27 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+          <t>Tầng 2 của AIS §4.2</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
+          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
         </is>
       </c>
     </row>
@@ -3371,17 +3491,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Tầng 2 của AIS §4.2</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -3391,7 +3511,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3401,17 +3521,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -3421,7 +3541,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3556,12 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3451,7 +3571,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3586,12 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3481,7 +3601,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3491,17 +3611,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3511,7 +3631,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
         </is>
       </c>
     </row>
@@ -3526,12 +3646,12 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán từ mẫu</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -3541,7 +3661,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3551,62 +3671,32 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F12"/>
+  <autoFilter ref="A1:F11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3779,17 +3869,17 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5 ✔</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Bộ đọc telemetry UART</t>
+          <t>Bộ đọc telemetry UART — XONG</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Đọc cổng nối tiếp theo khung tin có checksum + nhãn thời gian; có hạn chờ; ghi nguyên văn vào tệp để tái lập lại được</t>
+          <t>eaa telemetry: hạn thời gian bắt buộc, khung hỏng được đếm, bản nguyên văn giữ lại và phát lại được; diagnose run --port từ chối kết luận trên phiên không tin được. TC-43</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -3799,7 +3889,7 @@
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>eaa/telemetry.py (mới), phụ thuộc pyserial</t>
+          <t>eaa/telemetry.py, eaa/cli.py</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -859,22 +859,22 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="15">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8953488372093024</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>845</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>34 mục (SL-01..SL-34)</t>
+          <t>35 mục (SL-01..SL-35)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3340,8 +3340,68 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C77" s="20" t="inlineStr">
+        <is>
+          <t>Không dựng firmware chẩn đoán rỗng</t>
+        </is>
+      </c>
+      <c r="D77" s="20" t="inlineStr">
+        <is>
+          <t>Kịch bản chưa khai phần đo thì dừng — ảnh im lặng không phân biệt được với mạch hỏng</t>
+        </is>
+      </c>
+      <c r="E77" s="20" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="inlineStr">
+        <is>
+          <t>TC-44b</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>Checklist an toàn theo ảnh tới lúc nạp</t>
+        </is>
+      </c>
+      <c r="D78" s="20" t="inlineStr">
+        <is>
+          <t>Thẻ .meta.json đi kèm ảnh; eaa flash đưa checklist ra đúng lúc người bấm đồng ý</t>
+        </is>
+      </c>
+      <c r="E78" s="20" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py + eaa/cli.py</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>TC-44d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F76"/>
+  <autoFilter ref="A1:F78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3436,12 +3496,12 @@
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
+          <t>Bộ khung ở pack + phần đo ở dự án, ghép bằng liên kết; eaa diagnose build</t>
         </is>
       </c>
       <c r="E3" s="21" t="inlineStr">
@@ -3451,7 +3511,7 @@
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
+          <t>2/6 kịch bản đã có phần đo (DS-01, DS-04); bốn kịch bản còn lại báo rõ 'chưa khai phần đo' thay vì im lặng</t>
         </is>
       </c>
     </row>
@@ -3461,27 +3521,27 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Tầng 2 của AIS §4.2</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Một phần</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
         </is>
       </c>
     </row>
@@ -3491,17 +3551,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Tầng 2 của AIS §4.2</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -3511,7 +3571,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
         </is>
       </c>
     </row>
@@ -3521,17 +3581,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -3541,7 +3601,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3616,12 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3571,7 +3631,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3646,12 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3601,7 +3661,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
         </is>
       </c>
     </row>
@@ -3611,17 +3671,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán từ mẫu</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>diagnostics.yaml đã có trường firmware_template nhưng chưa nơi nào dùng</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3631,7 +3691,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Mỗi kịch bản DS-xx cần một firmware nhỏ tự in số đo ra UART</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3896,17 +3956,17 @@
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6 ✔</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán</t>
+          <t>Sinh firmware chẩn đoán — XONG (2/6 kịch bản)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Dùng firmware_template của từng kịch bản DS-xx để sinh firmware nhỏ tự in số đo</t>
+          <t>eaa diagnose build: bộ khung của pack + phần đo của dự án, ghép bằng liên kết. Ảnh mang thẻ an toàn tới tận lúc nạp. TC-44</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -3916,7 +3976,7 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa/firmware.py, packs/avr/templates/, projects/*/diagnostics/</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -859,13 +859,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="D14" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="9" t="n">
         <v>1</v>
@@ -874,7 +874,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.85</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="15">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>6</v>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.8953488372093024</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>868</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>35 mục (SL-01..SL-35)</t>
+          <t>36 mục (SL-01..SL-36)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3400,8 +3400,98 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+        </is>
+      </c>
+      <c r="D79" s="20" t="inlineStr">
+        <is>
+          <t>eaa tune --port thu telemetry, rút số đo theo tiêu chí đã khai, rồi phong hạng</t>
+        </is>
+      </c>
+      <c r="E79" s="20" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F79" s="20" t="inlineStr">
+        <is>
+          <t>TC-45 (23 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>Không phong hạng cho bản chưa từng chạy trên mạch</t>
+        </is>
+      </c>
+      <c r="D80" s="20" t="inlineStr">
+        <is>
+          <t>Nhật ký nạp nói bản khác đang trên chip thì CHẶN; nhật ký trống thì ghi device_verified=false chứ không cấm</t>
+        </is>
+      </c>
+      <c r="E80" s="20" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>TC-45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>Tiêu chí nghiệm thu có TRƯỚC số đo</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>acceptance.measurements khai trước; thiếu số đo hay vượt ngưỡng đều chặn phong hạng</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="inlineStr">
+        <is>
+          <t>constraints.yaml + eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F81" s="20" t="inlineStr">
+        <is>
+          <t>TC-45b, TC-45c, TC-45d</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F78"/>
+  <autoFilter ref="A1:F81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3412,7 +3502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3521,27 +3611,27 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Đường ống đã có ở hai đầu (diagnose, tune, versions) nhưng chưa nối liền</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+          <t>Tầng 2 của AIS §4.2</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Hiện phải nhập số đo bằng tay; nối được UART thì vòng này tự khép</t>
+          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
         </is>
       </c>
     </row>
@@ -3551,17 +3641,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Tầng 2 của AIS §4.2</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -3571,7 +3661,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3581,17 +3671,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -3601,7 +3691,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3706,12 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3631,7 +3721,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3736,12 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -3661,7 +3751,7 @@
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3671,17 +3761,17 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -3691,7 +3781,7 @@
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3701,62 +3791,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3983,17 +4043,17 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7 ✔</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Khép vòng số đo → G4</t>
+          <t>Khép vòng số đo → G4 — XONG</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Số đo từ UART chảy thẳng vào eaa tune; G4 duyệt thì phong hạng hw-verified</t>
+          <t>eaa tune --port: thu telemetry → rút số đo theo tiêu chí đã khai → G4 → hw-verified. Commit phong hạng phải là commit đang chạy trên thiết bị. TC-45</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -4003,7 +4063,7 @@
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>eaa/versions.py, eaa/cli.py</t>
+          <t>eaa/acceptance.py, eaa/cli.py</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -834,22 +834,22 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="14">
@@ -884,22 +884,22 @@
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -917,7 +917,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>900</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>36 mục (SL-01..SL-36)</t>
+          <t>37 mục (SL-01..SL-37)</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2896,27 +2896,27 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
+          <t>eaa decide dựng tập phương án; gate đòi --option, không lấy gợi ý làm mặc định</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa/options.py + eaa decide</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>TC-27 (33 test)</t>
+          <t>TC-46 (32 test)</t>
         </is>
       </c>
     </row>
@@ -2926,27 +2926,27 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
+          <t>Mỗi phương án phải nói mặt trái</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
+          <t>Thiếu cons là lỗi — danh sách toàn ưu điểm chỉ chuyển trách nhiệm sang người bấm</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>projects/*/diagnostics.yaml</t>
+          <t>eaa/options.py</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>TC-27</t>
+          <t>TC-46b</t>
         </is>
       </c>
     </row>
@@ -2956,27 +2956,27 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
+          <t>Mỗi phương án kèm rationale; gợi ý có lý do nhưng không thay quyết định</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa/options.py</t>
         </is>
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>TC-27</t>
+          <t>TC-46</t>
         </is>
       </c>
     </row>
@@ -2986,27 +2986,27 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>Biên dịch từng module rồi liên kết riêng</t>
+          <t>Phương án bị loại vẫn tra lại được</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
+          <t>Quyết định mang cả tập, kể cả cái bị loại; từ chối cả tập cũng được lưu</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>TC-40 (19 test)</t>
+          <t>TC-46d</t>
         </is>
       </c>
     </row>
@@ -3021,22 +3021,22 @@
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>Ráp ảnh nạp được (.elf → .hex)</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
+          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>TC-40c</t>
+          <t>TC-27 (33 test)</t>
         </is>
       </c>
     </row>
@@ -3051,22 +3051,22 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>Đo kích thước nói rõ đang đo tầm nào</t>
+          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
+          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py</t>
+          <t>projects/*/diagnostics.yaml</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>TC-40d</t>
+          <t>TC-27</t>
         </is>
       </c>
     </row>
@@ -3081,22 +3081,22 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
+          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
+          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
-          <t>TC-41e</t>
+          <t>TC-27</t>
         </is>
       </c>
     </row>
@@ -3111,22 +3111,22 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>Nạp firmware xuống mạch qua USB</t>
+          <t>Biên dịch từng module rồi liên kết riêng</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>eaa flash gọi năng lực flash của pack; bốn phép kiểm rồi mới hỏi người</t>
+          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>eaa/flash.py + eaa flash</t>
+          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>TC-42 (30 test)</t>
+          <t>TC-40 (19 test)</t>
         </is>
       </c>
     </row>
@@ -3141,22 +3141,22 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>Bốn phép kiểm trước khi nạp</t>
+          <t>Ráp ảnh nạp được (.elf → .hex)</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>Có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận — đều là 'không', không phải cảnh báo</t>
+          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>eaa/flash.py</t>
+          <t>eaa/tools/compile.py</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>TC-42b, TC-42c</t>
+          <t>TC-40c</t>
         </is>
       </c>
     </row>
@@ -3171,22 +3171,22 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>Nhật ký nạp append-only</t>
+          <t>Đo kích thước nói rõ đang đo tầm nào</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>Commit nào, ảnh nào (kèm băm), cổng nào, ai, lúc nào — ghi cả lần trượt</t>
+          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
         <is>
-          <t>eaa flash --history</t>
+          <t>eaa/tools/compile.py</t>
         </is>
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>TC-42d</t>
+          <t>TC-40d</t>
         </is>
       </c>
     </row>
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>Engine không đoán cổng để nạp</t>
+          <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Nhận ra đúng một cổng thì tự chọn; mơ hồ thì dừng và đòi --port</t>
+          <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>eaa/cli.py</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>TC-42e</t>
+          <t>TC-41e</t>
         </is>
       </c>
     </row>
@@ -3231,22 +3231,22 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>Đọc telemetry UART thật</t>
+          <t>Nạp firmware xuống mạch qua USB</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>eaa telemetry thu thẳng từ cổng; diagnose run --port dùng luôn kênh máy sống</t>
+          <t>eaa flash gọi năng lực flash của pack; bốn phép kiểm rồi mới hỏi người</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>eaa/telemetry.py</t>
+          <t>eaa/flash.py + eaa flash</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>TC-43 (28 test)</t>
+          <t>TC-42 (30 test)</t>
         </is>
       </c>
     </row>
@@ -3261,22 +3261,22 @@
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>Khung telemetry có checksum</t>
+          <t>Bốn phép kiểm trước khi nạp</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Định dạng khung do dự án khai; mỗi loại hỏng có lý do riêng</t>
+          <t>Có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận — đều là 'không', không phải cảnh báo</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>eaa/telemetry.py</t>
+          <t>eaa/flash.py</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>TC-43a</t>
+          <t>TC-42b, TC-42c</t>
         </is>
       </c>
     </row>
@@ -3291,22 +3291,22 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>Phiên thu nhiều khung hỏng bị từ chối</t>
+          <t>Nhật ký nạp append-only</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>Vượt ngưỡng thì không kết luận: dữ liệu nhiễu vẫn cho ra số trông hợp lý</t>
+          <t>Commit nào, ảnh nào (kèm băm), cổng nào, ai, lúc nào — ghi cả lần trượt</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>eaa/telemetry.py</t>
+          <t>eaa flash --history</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>TC-43c</t>
+          <t>TC-42d</t>
         </is>
       </c>
     </row>
@@ -3321,22 +3321,22 @@
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>Giữ nguyên văn bản thu, phát lại được</t>
+          <t>Engine không đoán cổng để nạp</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Bản thô cạnh bản đã lọc; phân tích lại không cần mạch</t>
+          <t>Nhận ra đúng một cổng thì tự chọn; mơ hồ thì dừng và đòi --port</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>eaa telemetry --replay</t>
+          <t>eaa/cli.py</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>TC-43d</t>
+          <t>TC-42e</t>
         </is>
       </c>
     </row>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>Không dựng firmware chẩn đoán rỗng</t>
+          <t>Đọc telemetry UART thật</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>Kịch bản chưa khai phần đo thì dừng — ảnh im lặng không phân biệt được với mạch hỏng</t>
+          <t>eaa telemetry thu thẳng từ cổng; diagnose run --port dùng luôn kênh máy sống</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py</t>
+          <t>eaa/telemetry.py</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>TC-44b</t>
+          <t>TC-43 (28 test)</t>
         </is>
       </c>
     </row>
@@ -3381,22 +3381,22 @@
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>Checklist an toàn theo ảnh tới lúc nạp</t>
+          <t>Khung telemetry có checksum</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>Thẻ .meta.json đi kèm ảnh; eaa flash đưa checklist ra đúng lúc người bấm đồng ý</t>
+          <t>Định dạng khung do dự án khai; mỗi loại hỏng có lý do riêng</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py + eaa/cli.py</t>
+          <t>eaa/telemetry.py</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
-          <t>TC-44d</t>
+          <t>TC-43a</t>
         </is>
       </c>
     </row>
@@ -3411,22 +3411,22 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>Phiên thu nhiều khung hỏng bị từ chối</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>eaa tune --port thu telemetry, rút số đo theo tiêu chí đã khai, rồi phong hạng</t>
+          <t>Vượt ngưỡng thì không kết luận: dữ liệu nhiễu vẫn cho ra số trông hợp lý</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
         <is>
-          <t>eaa/acceptance.py</t>
+          <t>eaa/telemetry.py</t>
         </is>
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>TC-45 (23 test)</t>
+          <t>TC-43c</t>
         </is>
       </c>
     </row>
@@ -3441,22 +3441,22 @@
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>Không phong hạng cho bản chưa từng chạy trên mạch</t>
+          <t>Giữ nguyên văn bản thu, phát lại được</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Nhật ký nạp nói bản khác đang trên chip thì CHẶN; nhật ký trống thì ghi device_verified=false chứ không cấm</t>
+          <t>Bản thô cạnh bản đã lọc; phân tích lại không cần mạch</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>eaa/acceptance.py</t>
+          <t>eaa telemetry --replay</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>TC-45a</t>
+          <t>TC-43d</t>
         </is>
       </c>
     </row>
@@ -3471,27 +3471,147 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
+          <t>Không dựng firmware chẩn đoán rỗng</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Kịch bản chưa khai phần đo thì dừng — ảnh im lặng không phân biệt được với mạch hỏng</t>
+        </is>
+      </c>
+      <c r="E81" s="20" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py</t>
+        </is>
+      </c>
+      <c r="F81" s="20" t="inlineStr">
+        <is>
+          <t>TC-44b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>Checklist an toàn theo ảnh tới lúc nạp</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>Thẻ .meta.json đi kèm ảnh; eaa flash đưa checklist ra đúng lúc người bấm đồng ý</t>
+        </is>
+      </c>
+      <c r="E82" s="20" t="inlineStr">
+        <is>
+          <t>eaa/firmware.py + eaa/cli.py</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>TC-44d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C83" s="20" t="inlineStr">
+        <is>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+        </is>
+      </c>
+      <c r="D83" s="20" t="inlineStr">
+        <is>
+          <t>eaa tune --port thu telemetry, rút số đo theo tiêu chí đã khai, rồi phong hạng</t>
+        </is>
+      </c>
+      <c r="E83" s="20" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F83" s="20" t="inlineStr">
+        <is>
+          <t>TC-45 (23 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C84" s="20" t="inlineStr">
+        <is>
+          <t>Không phong hạng cho bản chưa từng chạy trên mạch</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Nhật ký nạp nói bản khác đang trên chip thì CHẶN; nhật ký trống thì ghi device_verified=false chứ không cấm</t>
+        </is>
+      </c>
+      <c r="E84" s="20" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>TC-45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C85" s="20" t="inlineStr">
+        <is>
           <t>Tiêu chí nghiệm thu có TRƯỚC số đo</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>acceptance.measurements khai trước; thiếu số đo hay vượt ngưỡng đều chặn phong hạng</t>
         </is>
       </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="E85" s="20" t="inlineStr">
         <is>
           <t>constraints.yaml + eaa/acceptance.py</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F85" s="20" t="inlineStr">
         <is>
           <t>TC-45b, TC-45c, TC-45d</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F81"/>
+  <autoFilter ref="A1:F85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3502,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3676,12 +3796,12 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Hiện gate chỉ nhị phân duyệt/từ chối — không có 'ba cách làm, chọn một'</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -3691,7 +3811,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Cần GatePayload dạng nhiều lựa chọn + GateDecision ghi phương án đã chọn; đây là thứ gần nhất với điều bạn vừa nêu</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3701,17 +3821,17 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Kèm lập luận thiết kế vào hồ sơ gate, không chỉ kèm mã</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -3721,7 +3841,7 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Phụ thuộc mục trên; cùng một lượt làm thì gọn hơn</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3731,92 +3851,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4070,17 +4130,17 @@
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8 ✔</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Gate nhiều phương án</t>
+          <t>Gate nhiều phương án — XONG</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>GatePayload trình N cách làm kèm đánh đổi; GateDecision ghi phương án đã chọn và lý do; phương án bị loại vẫn lưu để tra lại</t>
+          <t>eaa decide dựng N phương án kèm đánh đổi; approve ĐÒI --option và không lấy gợi ý làm mặc định; cả tập (kể cả cái bị loại) vào quyết định. TC-46</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -4090,7 +4150,7 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py, eaa/cli.py</t>
+          <t>eaa/options.py, eaa/gates.py, eaa/cli.py</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,15 +52,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="009C0006"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F4E79"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -180,19 +180,19 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Vũ Trí Công · đề án Thạc sĩ Kỹ thuật, PTIT · cập nhật 2026-08-29</t>
+          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-08-30</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>B. Kiến trúc ba tầng</t>
+          <t>A. Khởi tạo &amp; phạm vi</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -674,42 +674,42 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>B. Kiến trúc ba tầng</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>1</v>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>D. Sinh mã</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>13</v>
@@ -717,77 +717,77 @@
       <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>1</v>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>F. Mô phỏng</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>0</v>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>F. Mô phỏng</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -795,8 +795,8 @@
       <c r="E11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>1</v>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
@@ -805,14 +805,14 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
@@ -820,8 +820,8 @@
       <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="6" t="n">
-        <v>0</v>
+      <c r="F12" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1</v>
@@ -830,207 +830,282 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>K. Bàn giao &amp; vận hành</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>L. Siêu nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="12" t="n">
+      <c r="B18" s="11" t="n">
+        <v>113</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="13" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="G18" s="13" t="n">
+        <v>0.9553571428571429</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Số liệu nền</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Test tự động đang xanh</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Dòng mã engine (eaa/)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>14.792</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Lệnh CLI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>Platform Pack</t>
+          <t>Test tự động đang xanh</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1 (AVR 8-bit)</t>
+          <t>900</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>Mô hình nền</t>
+          <t>Dòng mã engine (eaa/)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview (ghim phiên bản)</t>
+          <t>14.792</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
+          <t>Lệnh CLI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Platform Pack</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1 (AVR 8-bit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Mô hình nền</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gemini-3.1-pro-preview (ghim phiên bản)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
           <t>Sai lệch thiết kế đã ghi</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>37 mục (SL-01..SL-37)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Ý nghĩa bốn trạng thái</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Đã làm</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Có mã, có test, chạy được end-to-end</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Một phần</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Có mã nhưng còn mắt xích thiếu — xem cột 'Còn thiếu gì'</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Chưa có mã</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Cố ý không làm</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Làm được nhưng thiết kế cấm — xem cột 'Còn thiếu gì' để rõ điều khoản</t>
         </is>
@@ -1047,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1306,27 +1381,27 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>B. Kiến trúc ba tầng</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Kho ràng buộc + hồ sơ phần cứng + thư viện prompt</t>
+          <t>Thêm họ MCU mới không sửa engine (NFR-05)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>constraints.yaml, hardware_profile.yaml, prompt nền tảng theo pack</t>
+          <t>Pack thứ hai (STM32 Cortex-M4F) thêm vào KHÔNG sinh một nhánh rẽ nào trong eaa/</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>eaa/kb.py</t>
+          <t>packs/avr/ + packs/stm32/</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>test_kb.py</t>
+          <t>TC-47</t>
         </is>
       </c>
     </row>
@@ -1341,22 +1416,22 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>Knowledge Graph module→ngoại vi→thanh ghi→chunk</t>
+          <t>Kho ràng buộc + hồ sơ phần cứng + thư viện prompt</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Đồ thị tự dựng từ kho tri thức; khớp tên thanh ghi chính xác, không nhúng vector</t>
+          <t>constraints.yaml, hardware_profile.yaml, prompt nền tảng theo pack</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>eaa/graph.py</t>
+          <t>eaa/kb.py</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>TC-18 (31 test)</t>
+          <t>test_kb.py</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1446,12 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>Truy xuất chunk tất định</t>
+          <t>Knowledge Graph module→ngoại vi→thanh ghi→chunk</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Cùng câu hỏi cho cùng top-k; không phụ thuộc thứ tự ngẫu nhiên</t>
+          <t>Đồ thị tự dựng từ kho tri thức; khớp tên thanh ghi chính xác, không nhúng vector</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -1386,7 +1461,7 @@
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>TC-18</t>
+          <t>TC-18 (31 test)</t>
         </is>
       </c>
     </row>
@@ -1401,22 +1476,22 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>Nén ngữ cảnh K1–K7, ngân sách 8.000 token</t>
+          <t>Truy xuất chunk tất định</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>7 tầng có ngân sách con; cắt luật lỗi rồi tới interface, KHÔNG BAO GIỜ cắt chunk</t>
+          <t>Cùng câu hỏi cho cùng top-k; không phụ thuộc thứ tự ngẫu nhiên</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>eaa/composer.py</t>
+          <t>eaa/graph.py</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>TC-04 (36 test), TC-16</t>
+          <t>TC-18</t>
         </is>
       </c>
     </row>
@@ -1431,22 +1506,22 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>Bắt buộc trích dẫn // ref: &lt;chunk-id&gt;</t>
+          <t>Nén ngữ cảnh K1–K7, ngân sách 8.000 token</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Mã cấu hình thanh ghi không có trích dẫn thì cổng static chặn</t>
+          <t>7 tầng có ngân sách con; cắt luật lỗi rồi tới interface, KHÔNG BAO GIỜ cắt chunk</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/static.py</t>
+          <t>eaa/composer.py</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>TC-17</t>
+          <t>TC-04 (36 test), TC-16</t>
         </is>
       </c>
     </row>
@@ -1461,22 +1536,22 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>Append-only + supersede + stale set</t>
+          <t>Bắt buộc trích dẫn // ref: &lt;chunk-id&gt;</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Không ghi đè vật lý; chunk bị thay thì mã dùng nó bị đánh dấu cần xem lại</t>
+          <t>Mã cấu hình thanh ghi không có trích dẫn thì cổng static chặn</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>eaa/lifecycle.py</t>
+          <t>eaa/tools/static.py</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>TC-29 (23 test)</t>
+          <t>TC-17</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1566,12 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>Ba đường truy vấn ngược</t>
+          <t>Append-only + supersede + stale set</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>Từ chunk tìm ra mã: qua đồ thị, qua // ref:, qua trailer chunk-ids của commit</t>
+          <t>Không ghi đè vật lý; chunk bị thay thì mã dùng nó bị đánh dấu cần xem lại</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -1506,7 +1581,7 @@
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>TC-29</t>
+          <t>TC-29 (23 test)</t>
         </is>
       </c>
     </row>
@@ -1521,22 +1596,22 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>Nạp PDF thành proposed fact</t>
+          <t>Ba đường truy vấn ngược</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Trích đoạn luôn ở trạng thái 'proposed', phải qua G2 mới thành tri thức</t>
+          <t>Từ chunk tìm ra mã: qua đồ thị, qua // ref:, qua trailer chunk-ids của commit</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>eaa/ingest.py</t>
+          <t>eaa/lifecycle.py</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>TC-22 (44 test)</t>
+          <t>TC-29</t>
         </is>
       </c>
     </row>
@@ -1551,12 +1626,12 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>Nguồn web giới hạn miền nhà sản xuất</t>
+          <t>Nạp PDF thành proposed fact</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>So theo hậu tố tên miền, không so chuỗi con</t>
+          <t>Trích đoạn luôn ở trạng thái 'proposed', phải qua G2 mới thành tri thức</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -1566,7 +1641,7 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>TC-22</t>
+          <t>TC-22 (44 test)</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1656,12 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>Sổ giả định (Assumption Log)</t>
+          <t>Nguồn web giới hạn miền nhà sản xuất</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Giả định được ghi, và bị thay khi có số đo thật</t>
+          <t>So theo hậu tố tên miền, không so chuỗi con</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -1611,22 +1686,22 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>Tự đánh giá đủ thông tin (RIC)</t>
+          <t>Sổ giả định (Assumption Log)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>Trả về CÓ / THIẾU / MÂU THUẪN; chuẩn hóa số nên 0b00 == 0x00 == 0</t>
+          <t>Giả định được ghi, và bị thay khi có số đo thật</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
         <is>
-          <t>eaa/readiness.py</t>
+          <t>eaa/ingest.py</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>TC-24 (18 test)</t>
+          <t>TC-22</t>
         </is>
       </c>
     </row>
@@ -1636,27 +1711,27 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>D. Sinh mã</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>Vòng lặp chuẩn 13 bước</t>
+          <t>Tự đánh giá đủ thông tin (RIC)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Từ chọn module tới merge, mỗi bước ghi vết vào Project State</t>
+          <t>Trả về CÓ / THIẾU / MÂU THUẪN; chuẩn hóa số nên 0b00 == 0x00 == 0</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>eaa/orchestrator.py</t>
+          <t>eaa/readiness.py</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>TC-06 (28 test)</t>
+          <t>TC-24 (18 test)</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1746,12 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>Vòng tự sửa ≤ 3 lần, dạng patch</t>
+          <t>Vòng lặp chuẩn 13 bước</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>Gửi patch chứ không gửi lại cả tệp; quá 3 lần thì dừng và bàn giao người</t>
+          <t>Từ chọn module tới merge, mỗi bước ghi vết vào Project State</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -1686,7 +1761,7 @@
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>TC-06, TC-19</t>
+          <t>TC-06 (28 test)</t>
         </is>
       </c>
     </row>
@@ -1701,22 +1776,22 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>Kiểm ngân sách token TRƯỚC khi gọi mô hình</t>
+          <t>Vòng tự sửa ≤ 3 lần, dạng patch</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>count_tokens chạy trước; vượt ngân sách thì không gọi API</t>
+          <t>Gửi patch chứ không gửi lại cả tệp; quá 3 lần thì dừng và bàn giao người</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>eaa/llm/base.py</t>
+          <t>eaa/orchestrator.py</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>TC-16</t>
+          <t>TC-06, TC-19</t>
         </is>
       </c>
     </row>
@@ -1731,22 +1806,22 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>Adapter Gemini Pro 3.1 ghim phiên bản</t>
+          <t>Kiểm ngân sách token TRƯỚC khi gọi mô hình</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>REST thuần bằng urllib, stateless mỗi lần gọi, clamp output limit theo model thật</t>
+          <t>count_tokens chạy trước; vượt ngân sách thì không gọi API</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>eaa/llm/gemini.py</t>
+          <t>eaa/llm/base.py</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>TC-11 (31 test)</t>
+          <t>TC-16</t>
         </is>
       </c>
     </row>
@@ -1761,22 +1836,22 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>Lối gọi văn xuôi complete()</t>
+          <t>Adapter Gemini Pro 3.1 ghim phiên bản</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>Tra cứu / phân loại lỗi không phải sinh mã, nên không bị đòi khối ```file:</t>
+          <t>REST thuần bằng urllib, stateless mỗi lần gọi, clamp output limit theo model thật</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>eaa/llm/*.py</t>
+          <t>eaa/llm/gemini.py</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>TC-39</t>
+          <t>TC-11 (31 test)</t>
         </is>
       </c>
     </row>
@@ -1791,22 +1866,22 @@
       </c>
       <c r="C25" s="20" t="inlineStr">
         <is>
-          <t>MockLLM tất định cho Sprint 1–3</t>
+          <t>Lối gọi văn xuôi complete()</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Cùng interface với mô hình thật; kiểm thử tích hợp không tốn API</t>
+          <t>Tra cứu / phân loại lỗi không phải sinh mã, nên không bị đòi khối ```file:</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>eaa/llm/mock.py</t>
+          <t>eaa/llm/*.py</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>toàn bộ test tích hợp</t>
+          <t>TC-39</t>
         </is>
       </c>
     </row>
@@ -1821,22 +1896,22 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>Nhật ký lời gọi + phát lại</t>
+          <t>MockLLM tất định cho Sprint 1–3</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Lưu (băm prompt → phản hồi) làm bằng chứng; ReplayClient chạy lại không tốn API</t>
+          <t>Cùng interface với mô hình thật; kiểm thử tích hợp không tốn API</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>eaa/llm/calllog.py</t>
+          <t>eaa/llm/mock.py</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>TC-15</t>
+          <t>toàn bộ test tích hợp</t>
         </is>
       </c>
     </row>
@@ -1851,12 +1926,12 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>Phát hiện mô hình trôi hành vi</t>
+          <t>Nhật ký lời gọi + phát lại</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Cùng băm prompt mà hai phản hồi khác nhau thì hiện ra</t>
+          <t>Lưu (băm prompt → phản hồi) làm bằng chứng; ReplayClient chạy lại không tốn API</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -1881,22 +1956,22 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>Che khóa API ở mọi lối ra</t>
+          <t>Phát hiện mô hình trôi hành vi</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Không vào log, commit, repr, thông báo lỗi hay băm prompt</t>
+          <t>Cùng băm prompt mà hai phản hồi khác nhau thì hiện ra</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>eaa/llm/base.py</t>
+          <t>eaa/llm/calllog.py</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>TC-14</t>
+          <t>TC-15</t>
         </is>
       </c>
     </row>
@@ -1911,22 +1986,22 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
+          <t>Che khóa API ở mọi lối ra</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>Sinh vòng lặp chính từ khuôn của pack, dịch mọi module đã merge, liên kết, ra ảnh nạp được</t>
+          <t>Không vào log, commit, repr, thông báo lỗi hay băm prompt</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py + eaa build</t>
+          <t>eaa/llm/base.py</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>TC-41 (24 test)</t>
+          <t>TC-14</t>
         </is>
       </c>
     </row>
@@ -1941,22 +2016,22 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>Bộ định thời hợp tác</t>
+          <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>Bảng việc định kỳ; ngắt chỉ tăng bộ đếm, đọc bộ đếm trong khối nguyên tử</t>
+          <t>Sinh vòng lặp chính từ khuôn của pack, dịch mọi module đã merge, liên kết, ra ảnh nạp được</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>packs/avr/templates/main.c.tmpl</t>
+          <t>eaa/firmware.py + eaa build</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>TC-41</t>
+          <t>TC-41 (24 test)</t>
         </is>
       </c>
     </row>
@@ -1971,22 +2046,22 @@
       </c>
       <c r="C31" s="20" t="inlineStr">
         <is>
-          <t>Module đã merge không được bỏ quên khi ráp</t>
+          <t>Bộ định thời hợp tác</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>Merge mà vắng mặt trong firmware.yaml là LỖI; không chạy định kỳ thì khai step: null</t>
+          <t>Bảng việc định kỳ; ngắt chỉ tăng bộ đếm, đọc bộ đếm trong khối nguyên tử</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py</t>
+          <t>packs/avr/templates/main.c.tmpl</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>TC-41b</t>
+          <t>TC-41</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2076,12 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>Mã chưa merge không vào được firmware</t>
+          <t>Module đã merge không được bỏ quên khi ráp</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>Bản thiết kế ráp nhắc tới module chưa qua G3 thì dừng</t>
+          <t>Merge mà vắng mặt trong firmware.yaml là LỖI; không chạy định kỳ thì khai step: null</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -2016,7 +2091,7 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>TC-41c</t>
+          <t>TC-41b</t>
         </is>
       </c>
     </row>
@@ -2026,27 +2101,27 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>D. Sinh mã</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
         <is>
-          <t>Bốn cổng công cụ</t>
+          <t>Mã chưa merge không vào được firmware</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>compile, static, unittests, size — mỗi cổng trả ToolReport có bằng chứng</t>
+          <t>Bản thiết kế ráp nhắc tới module chưa qua G3 thì dừng</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>TC-07 (43 test)</t>
+          <t>TC-41c</t>
         </is>
       </c>
     </row>
@@ -2061,22 +2136,22 @@
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>Bất biến merge</t>
+          <t>Bốn cổng công cụ</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>Chỉ merge khi TOÀN BỘ ToolReport.passed VÀ G3 duyệt; không có nhánh thứ hai</t>
+          <t>compile, static, unittests, size — mỗi cổng trả ToolReport có bằng chứng</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
-          <t>eaa/vcs.py + orchestrator</t>
+          <t>eaa/tools/</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>TC-01 (45 test)</t>
+          <t>TC-07 (43 test)</t>
         </is>
       </c>
     </row>
@@ -2091,22 +2166,22 @@
       </c>
       <c r="C35" s="20" t="inlineStr">
         <is>
-          <t>Băm nội dung xuyên suốt</t>
+          <t>Bất biến merge</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>Hồ sơ gate → quyết định → ủy quyền merge cùng một băm: người duyệt X thì merge đúng X</t>
+          <t>Chỉ merge khi TOÀN BỘ ToolReport.passed VÀ G3 duyệt; không có nhánh thứ hai</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py, eaa/vcs.py</t>
+          <t>eaa/vcs.py + orchestrator</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-01 (45 test)</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2196,22 @@
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>5 Human Gate không vượt được</t>
+          <t>Băm nội dung xuyên suốt</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>Không có cờ --yes / --force / --skip-gate nào tồn tại trong CLI</t>
+          <t>Hồ sơ gate → quyết định → ủy quyền merge cùng một băm: người duyệt X thì merge đúng X</t>
         </is>
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/gates.py, eaa/vcs.py</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>TC-01, TC-28, TC-34</t>
+          <t>TC-01</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2226,12 @@
       </c>
       <c r="C37" s="20" t="inlineStr">
         <is>
-          <t>Phiên không có người ≠ người đồng ý</t>
+          <t>5 Human Gate không vượt được</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
         <is>
-          <t>Không phải TTY thì ném GateNotInteractive chứ không mặc định duyệt</t>
+          <t>Không có cờ --yes / --force / --skip-gate nào tồn tại trong CLI</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -2166,7 +2241,7 @@
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>TC-28</t>
+          <t>TC-01, TC-28, TC-34</t>
         </is>
       </c>
     </row>
@@ -2181,22 +2256,22 @@
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình không đi vào vòng tự sửa</t>
+          <t>Phiên không có người ≠ người đồng ý</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>Thiếu luật, thiếu công cụ → chặn ngay, không đốt 3 lượt sửa vô ích</t>
+          <t>Không phải TTY thì ném GateNotInteractive chứ không mặc định duyệt</t>
         </is>
       </c>
       <c r="E38" s="20" t="inlineStr">
         <is>
-          <t>eaa/orchestrator.py</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>TC-06</t>
+          <t>TC-28</t>
         </is>
       </c>
     </row>
@@ -2211,22 +2286,22 @@
       </c>
       <c r="C39" s="20" t="inlineStr">
         <is>
-          <t>Sổ lỗi ảo giác</t>
+          <t>Lỗi cấu hình không đi vào vòng tự sửa</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
         <is>
-          <t>Append-only; phân xử ghi thành sự kiện mới chứ không sửa sự kiện cũ</t>
+          <t>Thiếu luật, thiếu công cụ → chặn ngay, không đốt 3 lượt sửa vô ích</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
         <is>
-          <t>eaa/ledger.py</t>
+          <t>eaa/orchestrator.py</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>TC-10 (20 test)</t>
+          <t>TC-06</t>
         </is>
       </c>
     </row>
@@ -2241,22 +2316,22 @@
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>Báo cáo KPI</t>
+          <t>Sổ lỗi ảo giác</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>Tỉ lệ qua cổng, số lượt tự sửa, token tiêu thụ theo module</t>
+          <t>Append-only; phân xử ghi thành sự kiện mới chứ không sửa sự kiện cũ</t>
         </is>
       </c>
       <c r="E40" s="20" t="inlineStr">
         <is>
-          <t>eaa/kpi.py + eaa report</t>
+          <t>eaa/ledger.py</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>TC-09</t>
+          <t>TC-10 (20 test)</t>
         </is>
       </c>
     </row>
@@ -2266,27 +2341,27 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>F. Mô phỏng</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
         <is>
-          <t>Mô hình con lắc ngược + MIL</t>
+          <t>Báo cáo KPI</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
         <is>
-          <t>Mô phỏng động lực học, đánh giá theo tiêu chí nghiệm thu</t>
+          <t>Tỉ lệ qua cổng, số lượt tự sửa, token tiêu thụ theo module</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/sim.py, sim_runner.py</t>
+          <t>eaa/kpi.py + eaa report</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>TC-12 (12 test)</t>
+          <t>TC-09</t>
         </is>
       </c>
     </row>
@@ -2301,22 +2376,22 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>Quét tham số</t>
+          <t>Mô hình con lắc ngược + MIL</t>
         </is>
       </c>
       <c r="D42" s="20" t="inlineStr">
         <is>
-          <t>Quét lưới bộ tham số điều khiển, xếp hạng theo chỉ số</t>
+          <t>Mô phỏng động lực học, đánh giá theo tiêu chí nghiệm thu</t>
         </is>
       </c>
       <c r="E42" s="20" t="inlineStr">
         <is>
-          <t>eaa sim --sweep</t>
+          <t>eaa/tools/sim.py, sim_runner.py</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>TC-12</t>
+          <t>TC-12 (12 test)</t>
         </is>
       </c>
     </row>
@@ -2331,22 +2406,22 @@
       </c>
       <c r="C43" s="20" t="inlineStr">
         <is>
-          <t>Chỉ số thời gian ổn định đo đúng</t>
+          <t>Quét tham số</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>Đo từ lần cuối tín hiệu rời dải, tính từ lúc nhiễu kết thúc</t>
+          <t>Quét lưới bộ tham số điều khiển, xếp hạng theo chỉ số</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/sim.py</t>
+          <t>eaa sim --sweep</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>test_sim_verification.py</t>
+          <t>TC-12</t>
         </is>
       </c>
     </row>
@@ -2356,27 +2431,27 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>G. Công cụ &amp; môi trường</t>
+          <t>F. Mô phỏng</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>Chế độ 1 — quét công cụ đã có</t>
+          <t>Chỉ số thời gian ổn định đo đúng</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Có gì trên máy, phiên bản bao nhiêu, thiếu thì chặn cổng nào</t>
+          <t>Đo từ lần cuối tín hiệu rời dải, tính từ lúc nhiễu kết thúc</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>eaa doctor</t>
+          <t>eaa/tools/sim.py</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>TC-34 (37 test)</t>
+          <t>test_sim_verification.py</t>
         </is>
       </c>
     </row>
@@ -2391,22 +2466,22 @@
       </c>
       <c r="C45" s="20" t="inlineStr">
         <is>
-          <t>Chế độ 2 — sinh lệnh cài</t>
+          <t>Chế độ 1 — quét công cụ đã có</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>Sinh đúng lệnh theo hệ điều hành, hỏi người trước từng lệnh</t>
+          <t>Có gì trên máy, phiên bản bao nhiêu, thiếu thì chặn cổng nào</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
         <is>
-          <t>eaa doctor --fix</t>
+          <t>eaa doctor</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
-          <t>TC-34, TC-37</t>
+          <t>TC-34 (37 test)</t>
         </is>
       </c>
     </row>
@@ -2421,22 +2496,22 @@
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>Chế độ 3 — TỰ TÌM công cụ chưa biết</t>
+          <t>Chế độ 2 — sinh lệnh cài</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Phát hiện → tra cứu bằng mô hình → đề xuất; đây là phần vừa làm xong</t>
+          <t>Sinh đúng lệnh theo hệ điều hành, hỏi người trước từng lệnh</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>eaa/toolsearch.py</t>
+          <t>eaa doctor --fix</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>TC-39 (29 test)</t>
+          <t>TC-34, TC-37</t>
         </is>
       </c>
     </row>
@@ -2451,12 +2526,12 @@
       </c>
       <c r="C47" s="20" t="inlineStr">
         <is>
-          <t>Nhu cầu công cụ suy từ Platform Pack</t>
+          <t>Chế độ 3 — TỰ TÌM công cụ chưa biết</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>Không chép tay danh sách: pack.yaml đã ghi mọi chương trình nó gọi</t>
+          <t>Phát hiện → tra cứu bằng mô hình → đề xuất; đây là phần vừa làm xong</t>
         </is>
       </c>
       <c r="E47" s="20" t="inlineStr">
@@ -2466,7 +2541,7 @@
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>TC-39</t>
+          <t>TC-39 (29 test)</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2556,12 @@
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>Kiểm nguồn cài trước khi tới tay người</t>
+          <t>Nhu cầu công cụ suy từ Platform Pack</t>
         </is>
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>10 trình quản lý gói chính thống; tải trực tiếp phải HTTPS + miền cho phép + sha256</t>
+          <t>Không chép tay danh sách: pack.yaml đã ghi mọi chương trình nó gọi</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
@@ -2511,17 +2586,17 @@
       </c>
       <c r="C49" s="20" t="inlineStr">
         <is>
-          <t>Đề xuất công cụ vào manifest qua G2</t>
+          <t>Kiểm nguồn cài trước khi tới tay người</t>
         </is>
       </c>
       <c r="D49" s="20" t="inlineStr">
         <is>
-          <t>Append + supersede, mang theo approved_by / approved_at</t>
+          <t>10 trình quản lý gói chính thống; tải trực tiếp phải HTTPS + miền cho phép + sha256</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
         <is>
-          <t>eaa gate approve G2</t>
+          <t>eaa/toolsearch.py</t>
         </is>
       </c>
       <c r="F49" s="20" t="inlineStr">
@@ -2541,17 +2616,17 @@
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>Ràng buộc phiên bản của pack đè lên đề xuất</t>
+          <t>Đề xuất công cụ vào manifest qua G2</t>
         </is>
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>pack.yaml ghi avr-gcc &gt;=12.0, mô hình đề xuất 7.3 — lấy theo pack</t>
+          <t>Append + supersede, mang theo approved_by / approved_at</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>eaa/toolsearch.py</t>
+          <t>eaa gate approve G2</t>
         </is>
       </c>
       <c r="F50" s="20" t="inlineStr">
@@ -2571,22 +2646,22 @@
       </c>
       <c r="C51" s="20" t="inlineStr">
         <is>
-          <t>Khóa môi trường + cảnh báo trôi</t>
+          <t>Ràng buộc phiên bản của pack đè lên đề xuất</t>
         </is>
       </c>
       <c r="D51" s="20" t="inlineStr">
         <is>
-          <t>env_lock.json; toolchain đổi phiên bản thì cảnh báo trước khi so sánh A/B</t>
+          <t>pack.yaml ghi avr-gcc &gt;=12.0, mô hình đề xuất 7.3 — lấy theo pack</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
         <is>
-          <t>eaa/doctor.py</t>
+          <t>eaa/toolsearch.py</t>
         </is>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
-          <t>TC-36</t>
+          <t>TC-39</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2676,12 @@
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>Thẻ công cụ</t>
+          <t>Khóa môi trường + cảnh báo trôi</t>
         </is>
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Cú pháp gọi, cách đọc dòng lỗi, phiên bản đã xác nhận</t>
+          <t>env_lock.json; toolchain đổi phiên bản thì cảnh báo trước khi so sánh A/B</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
@@ -2616,7 +2691,7 @@
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
-          <t>TC-37</t>
+          <t>TC-36</t>
         </is>
       </c>
     </row>
@@ -2631,22 +2706,22 @@
       </c>
       <c r="C53" s="20" t="inlineStr">
         <is>
-          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
+          <t>Thẻ công cụ</t>
         </is>
       </c>
       <c r="D53" s="20" t="inlineStr">
         <is>
-          <t>Liệt kê cổng nối tiếp, khớp VID/PID với bo dự án khai; không đọc được thì nói thẳng</t>
+          <t>Cú pháp gọi, cách đọc dòng lỗi, phiên bản đã xác nhận</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
         <is>
-          <t>eaa/serialport.py + eaa ports</t>
+          <t>eaa/doctor.py</t>
         </is>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>TC-42a (8 test)</t>
+          <t>TC-37</t>
         </is>
       </c>
     </row>
@@ -2656,27 +2731,27 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>H. Phiên bản mã</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>Ba hạng chất lượng</t>
+          <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
         </is>
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
+          <t>Liệt kê cổng nối tiếp, khớp VID/PID với bo dự án khai; không đọc được thì nói thẳng</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>eaa/versions.py</t>
+          <t>eaa/serialport.py + eaa ports</t>
         </is>
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>TC-30 (26 test)</t>
+          <t>TC-42a (8 test)</t>
         </is>
       </c>
     </row>
@@ -2691,12 +2766,12 @@
       </c>
       <c r="C55" s="20" t="inlineStr">
         <is>
-          <t>known_good.lock chỉ cập nhật tại G4</t>
+          <t>Ba hạng chất lượng</t>
         </is>
       </c>
       <c r="D55" s="20" t="inlineStr">
         <is>
-          <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
+          <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
@@ -2706,7 +2781,7 @@
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>TC-30</t>
+          <t>TC-30 (26 test)</t>
         </is>
       </c>
     </row>
@@ -2721,17 +2796,17 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>Quay lui về bản known-good</t>
+          <t>known_good.lock chỉ cập nhật tại G4</t>
         </is>
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Rollback không làm mất bản known-good đang giữ</t>
+          <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>eaa rollback</t>
+          <t>eaa/versions.py</t>
         </is>
       </c>
       <c r="F56" s="20" t="inlineStr">
@@ -2751,22 +2826,22 @@
       </c>
       <c r="C57" s="20" t="inlineStr">
         <is>
-          <t>Commit truy vết đầy đủ (NFR-07)</t>
+          <t>Quay lui về bản known-good</t>
         </is>
       </c>
       <c r="D57" s="20" t="inlineStr">
         <is>
-          <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
+          <t>Rollback không làm mất bản known-good đang giữ</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
         <is>
-          <t>eaa/vcs.py</t>
+          <t>eaa rollback</t>
         </is>
       </c>
       <c r="F57" s="20" t="inlineStr">
         <is>
-          <t>TC-01</t>
+          <t>TC-30</t>
         </is>
       </c>
     </row>
@@ -2781,22 +2856,22 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>Kho phẩm xuất</t>
+          <t>Commit truy vết đầy đủ (NFR-07)</t>
         </is>
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
+          <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>eaa docs</t>
+          <t>eaa/vcs.py</t>
         </is>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
-          <t>TC-32 (33 test)</t>
+          <t>TC-01</t>
         </is>
       </c>
     </row>
@@ -2806,27 +2881,27 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>H. Phiên bản mã</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
         <is>
-          <t>17 lệnh CLI phủ 10 use case</t>
+          <t>Kho phẩm xuất</t>
         </is>
       </c>
       <c r="D59" s="20" t="inlineStr">
         <is>
-          <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
+          <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
         <is>
-          <t>eaa/cli.py</t>
+          <t>eaa docs</t>
         </is>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
-          <t>test_cli_e2e.py</t>
+          <t>TC-32 (33 test)</t>
         </is>
       </c>
     </row>
@@ -2841,22 +2916,22 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>Hồ sơ gate đủ để quyết định</t>
+          <t>17 lệnh CLI phủ 10 use case</t>
         </is>
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
+          <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/cli.py</t>
         </is>
       </c>
       <c r="F60" s="20" t="inlineStr">
         <is>
-          <t>TC-01, TC-28</t>
+          <t>test_cli_e2e.py</t>
         </is>
       </c>
     </row>
@@ -2871,12 +2946,12 @@
       </c>
       <c r="C61" s="20" t="inlineStr">
         <is>
-          <t>Từ chối phải có lý do</t>
+          <t>Hồ sơ gate đủ để quyết định</t>
         </is>
       </c>
       <c r="D61" s="20" t="inlineStr">
         <is>
-          <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
+          <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -2886,7 +2961,7 @@
       </c>
       <c r="F61" s="20" t="inlineStr">
         <is>
-          <t>TC-28</t>
+          <t>TC-01, TC-28</t>
         </is>
       </c>
     </row>
@@ -2901,22 +2976,22 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>Trình NHIỀU phương án để người chọn</t>
+          <t>Từ chối phải có lý do</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>eaa decide dựng tập phương án; gate đòi --option, không lấy gợi ý làm mặc định</t>
+          <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>eaa/options.py + eaa decide</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F62" s="20" t="inlineStr">
         <is>
-          <t>TC-46 (32 test)</t>
+          <t>TC-28</t>
         </is>
       </c>
     </row>
@@ -2931,22 +3006,22 @@
       </c>
       <c r="C63" s="20" t="inlineStr">
         <is>
-          <t>Mỗi phương án phải nói mặt trái</t>
+          <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
       <c r="D63" s="20" t="inlineStr">
         <is>
-          <t>Thiếu cons là lỗi — danh sách toàn ưu điểm chỉ chuyển trách nhiệm sang người bấm</t>
+          <t>eaa decide dựng tập phương án; gate đòi --option, không lấy gợi ý làm mặc định</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>eaa/options.py</t>
+          <t>eaa/options.py + eaa decide</t>
         </is>
       </c>
       <c r="F63" s="20" t="inlineStr">
         <is>
-          <t>TC-46b</t>
+          <t>TC-46 (32 test)</t>
         </is>
       </c>
     </row>
@@ -2961,12 +3036,12 @@
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
+          <t>Mỗi phương án phải nói mặt trái</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
         <is>
-          <t>Mỗi phương án kèm rationale; gợi ý có lý do nhưng không thay quyết định</t>
+          <t>Thiếu cons là lỗi — danh sách toàn ưu điểm chỉ chuyển trách nhiệm sang người bấm</t>
         </is>
       </c>
       <c r="E64" s="20" t="inlineStr">
@@ -2976,7 +3051,7 @@
       </c>
       <c r="F64" s="20" t="inlineStr">
         <is>
-          <t>TC-46</t>
+          <t>TC-46b</t>
         </is>
       </c>
     </row>
@@ -2991,22 +3066,22 @@
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>Phương án bị loại vẫn tra lại được</t>
+          <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
       <c r="D65" s="20" t="inlineStr">
         <is>
-          <t>Quyết định mang cả tập, kể cả cái bị loại; từ chối cả tập cũng được lưu</t>
+          <t>Mỗi phương án kèm rationale; gợi ý có lý do nhưng không thay quyết định</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
         <is>
-          <t>eaa/gates.py</t>
+          <t>eaa/options.py</t>
         </is>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
-          <t>TC-46d</t>
+          <t>TC-46</t>
         </is>
       </c>
     </row>
@@ -3016,27 +3091,27 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>Chẩn đoán hai kênh</t>
+          <t>Phương án bị loại vẫn tra lại được</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
         <is>
-          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
+          <t>Quyết định mang cả tập, kể cả cái bị loại; từ chối cả tập cũng được lưu</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>eaa/gates.py</t>
         </is>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>TC-27 (33 test)</t>
+          <t>TC-46d</t>
         </is>
       </c>
     </row>
@@ -3051,22 +3126,22 @@
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
+          <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
       <c r="D67" s="20" t="inlineStr">
         <is>
-          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
+          <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
         <is>
-          <t>projects/*/diagnostics.yaml</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>TC-27</t>
+          <t>TC-27 (33 test)</t>
         </is>
       </c>
     </row>
@@ -3081,17 +3156,17 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
+          <t>Bộ kịch bản chẩn đoán DS-01..06</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
         <is>
-          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
+          <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>eaa/diagnostics.py</t>
+          <t>projects/*/diagnostics.yaml</t>
         </is>
       </c>
       <c r="F68" s="20" t="inlineStr">
@@ -3111,22 +3186,22 @@
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>Biên dịch từng module rồi liên kết riêng</t>
+          <t>Checklist an toàn trước kịch bản gây chuyển động</t>
         </is>
       </c>
       <c r="D69" s="20" t="inlineStr">
         <is>
-          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
+          <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
+          <t>eaa/diagnostics.py</t>
         </is>
       </c>
       <c r="F69" s="20" t="inlineStr">
         <is>
-          <t>TC-40 (19 test)</t>
+          <t>TC-27</t>
         </is>
       </c>
     </row>
@@ -3141,22 +3216,22 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>Ráp ảnh nạp được (.elf → .hex)</t>
+          <t>Biên dịch từng module rồi liên kết riêng</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
         <is>
-          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
+          <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>eaa/tools/compile.py</t>
+          <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
         </is>
       </c>
       <c r="F70" s="20" t="inlineStr">
         <is>
-          <t>TC-40c</t>
+          <t>TC-40 (19 test)</t>
         </is>
       </c>
     </row>
@@ -3171,12 +3246,12 @@
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>Đo kích thước nói rõ đang đo tầm nào</t>
+          <t>Ráp ảnh nạp được (.elf → .hex)</t>
         </is>
       </c>
       <c r="D71" s="20" t="inlineStr">
         <is>
-          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
+          <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
@@ -3186,7 +3261,7 @@
       </c>
       <c r="F71" s="20" t="inlineStr">
         <is>
-          <t>TC-40d</t>
+          <t>TC-40c</t>
         </is>
       </c>
     </row>
@@ -3201,22 +3276,22 @@
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
+          <t>Đo kích thước nói rõ đang đo tầm nào</t>
         </is>
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
+          <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py</t>
+          <t>eaa/tools/compile.py</t>
         </is>
       </c>
       <c r="F72" s="20" t="inlineStr">
         <is>
-          <t>TC-41e</t>
+          <t>TC-40d</t>
         </is>
       </c>
     </row>
@@ -3231,22 +3306,22 @@
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>Nạp firmware xuống mạch qua USB</t>
+          <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
         </is>
       </c>
       <c r="D73" s="20" t="inlineStr">
         <is>
-          <t>eaa flash gọi năng lực flash của pack; bốn phép kiểm rồi mới hỏi người</t>
+          <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
         <is>
-          <t>eaa/flash.py + eaa flash</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>TC-42 (30 test)</t>
+          <t>TC-41e</t>
         </is>
       </c>
     </row>
@@ -3261,22 +3336,22 @@
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>Bốn phép kiểm trước khi nạp</t>
+          <t>Nạp firmware xuống mạch qua USB</t>
         </is>
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận — đều là 'không', không phải cảnh báo</t>
+          <t>eaa flash gọi năng lực flash của pack; bốn phép kiểm rồi mới hỏi người</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>eaa/flash.py</t>
+          <t>eaa/flash.py + eaa flash</t>
         </is>
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>TC-42b, TC-42c</t>
+          <t>TC-42 (30 test)</t>
         </is>
       </c>
     </row>
@@ -3291,22 +3366,22 @@
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>Nhật ký nạp append-only</t>
+          <t>Bốn phép kiểm trước khi nạp</t>
         </is>
       </c>
       <c r="D75" s="20" t="inlineStr">
         <is>
-          <t>Commit nào, ảnh nào (kèm băm), cổng nào, ai, lúc nào — ghi cả lần trượt</t>
+          <t>Có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận — đều là 'không', không phải cảnh báo</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>eaa flash --history</t>
+          <t>eaa/flash.py</t>
         </is>
       </c>
       <c r="F75" s="20" t="inlineStr">
         <is>
-          <t>TC-42d</t>
+          <t>TC-42b, TC-42c</t>
         </is>
       </c>
     </row>
@@ -3321,22 +3396,22 @@
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>Engine không đoán cổng để nạp</t>
+          <t>Nhật ký nạp append-only</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Nhận ra đúng một cổng thì tự chọn; mơ hồ thì dừng và đòi --port</t>
+          <t>Commit nào, ảnh nào (kèm băm), cổng nào, ai, lúc nào — ghi cả lần trượt</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>eaa/cli.py</t>
+          <t>eaa flash --history</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>TC-42e</t>
+          <t>TC-42d</t>
         </is>
       </c>
     </row>
@@ -3351,22 +3426,22 @@
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>Đọc telemetry UART thật</t>
+          <t>Engine không đoán cổng để nạp</t>
         </is>
       </c>
       <c r="D77" s="20" t="inlineStr">
         <is>
-          <t>eaa telemetry thu thẳng từ cổng; diagnose run --port dùng luôn kênh máy sống</t>
+          <t>Nhận ra đúng một cổng thì tự chọn; mơ hồ thì dừng và đòi --port</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>eaa/telemetry.py</t>
+          <t>eaa/cli.py</t>
         </is>
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>TC-43 (28 test)</t>
+          <t>TC-42e</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3456,12 @@
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>Khung telemetry có checksum</t>
+          <t>Đọc telemetry UART thật</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
         <is>
-          <t>Định dạng khung do dự án khai; mỗi loại hỏng có lý do riêng</t>
+          <t>eaa telemetry thu thẳng từ cổng; diagnose run --port dùng luôn kênh máy sống</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
@@ -3396,7 +3471,7 @@
       </c>
       <c r="F78" s="20" t="inlineStr">
         <is>
-          <t>TC-43a</t>
+          <t>TC-43 (28 test)</t>
         </is>
       </c>
     </row>
@@ -3411,12 +3486,12 @@
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>Phiên thu nhiều khung hỏng bị từ chối</t>
+          <t>Khung telemetry có checksum</t>
         </is>
       </c>
       <c r="D79" s="20" t="inlineStr">
         <is>
-          <t>Vượt ngưỡng thì không kết luận: dữ liệu nhiễu vẫn cho ra số trông hợp lý</t>
+          <t>Định dạng khung do dự án khai; mỗi loại hỏng có lý do riêng</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
@@ -3426,7 +3501,7 @@
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>TC-43c</t>
+          <t>TC-43a</t>
         </is>
       </c>
     </row>
@@ -3441,22 +3516,22 @@
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>Giữ nguyên văn bản thu, phát lại được</t>
+          <t>Phiên thu nhiều khung hỏng bị từ chối</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
         <is>
-          <t>Bản thô cạnh bản đã lọc; phân tích lại không cần mạch</t>
+          <t>Vượt ngưỡng thì không kết luận: dữ liệu nhiễu vẫn cho ra số trông hợp lý</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>eaa telemetry --replay</t>
+          <t>eaa/telemetry.py</t>
         </is>
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>TC-43d</t>
+          <t>TC-43c</t>
         </is>
       </c>
     </row>
@@ -3471,22 +3546,22 @@
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>Không dựng firmware chẩn đoán rỗng</t>
+          <t>Giữ nguyên văn bản thu, phát lại được</t>
         </is>
       </c>
       <c r="D81" s="20" t="inlineStr">
         <is>
-          <t>Kịch bản chưa khai phần đo thì dừng — ảnh im lặng không phân biệt được với mạch hỏng</t>
+          <t>Bản thô cạnh bản đã lọc; phân tích lại không cần mạch</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py</t>
+          <t>eaa telemetry --replay</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
         <is>
-          <t>TC-44b</t>
+          <t>TC-43d</t>
         </is>
       </c>
     </row>
@@ -3501,22 +3576,22 @@
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>Checklist an toàn theo ảnh tới lúc nạp</t>
+          <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
         <is>
-          <t>Thẻ .meta.json đi kèm ảnh; eaa flash đưa checklist ra đúng lúc người bấm đồng ý</t>
+          <t>Bộ khung ở pack + phần đo ở dự án, ghép bằng liên kết; eaa diagnose build</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>eaa/firmware.py + eaa/cli.py</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>TC-44d</t>
+          <t>TC-44, TC-58a</t>
         </is>
       </c>
     </row>
@@ -3531,22 +3606,22 @@
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+          <t>Không dựng firmware chẩn đoán rỗng</t>
         </is>
       </c>
       <c r="D83" s="20" t="inlineStr">
         <is>
-          <t>eaa tune --port thu telemetry, rút số đo theo tiêu chí đã khai, rồi phong hạng</t>
+          <t>Kịch bản chưa khai phần đo thì dừng — ảnh im lặng không phân biệt được với mạch hỏng</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>eaa/acceptance.py</t>
+          <t>eaa/firmware.py</t>
         </is>
       </c>
       <c r="F83" s="20" t="inlineStr">
         <is>
-          <t>TC-45 (23 test)</t>
+          <t>TC-44b</t>
         </is>
       </c>
     </row>
@@ -3561,22 +3636,22 @@
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>Không phong hạng cho bản chưa từng chạy trên mạch</t>
+          <t>Checklist an toàn theo ảnh tới lúc nạp</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>Nhật ký nạp nói bản khác đang trên chip thì CHẶN; nhật ký trống thì ghi device_verified=false chứ không cấm</t>
+          <t>Thẻ .meta.json đi kèm ảnh; eaa flash đưa checklist ra đúng lúc người bấm đồng ý</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>eaa/acceptance.py</t>
+          <t>eaa/firmware.py + eaa/cli.py</t>
         </is>
       </c>
       <c r="F84" s="20" t="inlineStr">
         <is>
-          <t>TC-45a</t>
+          <t>TC-44d</t>
         </is>
       </c>
     </row>
@@ -3591,27 +3666,717 @@
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
+          <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>eaa tune --port thu telemetry, rút số đo theo tiêu chí đã khai, rồi phong hạng</t>
+        </is>
+      </c>
+      <c r="E85" s="20" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="inlineStr">
+        <is>
+          <t>TC-45 (23 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="20" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C86" s="20" t="inlineStr">
+        <is>
+          <t>Không phong hạng cho bản chưa từng chạy trên mạch</t>
+        </is>
+      </c>
+      <c r="D86" s="20" t="inlineStr">
+        <is>
+          <t>Nhật ký nạp nói bản khác đang trên chip thì CHẶN; nhật ký trống thì ghi device_verified=false chứ không cấm</t>
+        </is>
+      </c>
+      <c r="E86" s="20" t="inlineStr">
+        <is>
+          <t>eaa/acceptance.py</t>
+        </is>
+      </c>
+      <c r="F86" s="20" t="inlineStr">
+        <is>
+          <t>TC-45a</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C87" s="20" t="inlineStr">
+        <is>
           <t>Tiêu chí nghiệm thu có TRƯỚC số đo</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D87" s="20" t="inlineStr">
         <is>
           <t>acceptance.measurements khai trước; thiếu số đo hay vượt ngưỡng đều chặn phong hạng</t>
         </is>
       </c>
-      <c r="E85" s="20" t="inlineStr">
+      <c r="E87" s="20" t="inlineStr">
         <is>
           <t>constraints.yaml + eaa/acceptance.py</t>
         </is>
       </c>
-      <c r="F85" s="20" t="inlineStr">
+      <c r="F87" s="20" t="inlineStr">
         <is>
           <t>TC-45b, TC-45c, TC-45d</t>
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="20" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C88" s="20" t="inlineStr">
+        <is>
+          <t>Kiểm sau khi nạp: đọc ngược bộ nhớ</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>Ba kết cục — khớp / lệch (lần nạp bị coi là trượt) / không kiểm được; 'nạp không báo lỗi' KHÔNG được đọc thành 'nạp đúng'</t>
+        </is>
+      </c>
+      <c r="E88" s="20" t="inlineStr">
+        <is>
+          <t>eaa/flash.py + năng lực flash_verify</t>
+        </is>
+      </c>
+      <c r="F88" s="20" t="inlineStr">
+        <is>
+          <t>TC-52 (12 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C89" s="20" t="inlineStr">
+        <is>
+          <t>Đo tay bằng dụng cụ — kênh thứ ba</t>
+        </is>
+      </c>
+      <c r="D89" s="20" t="inlineStr">
+        <is>
+          <t>Dòng tổng, sụt áp trên dây, nhiệt độ vỏ: hướng dẫn đích danh đo cái gì, ở đâu, điều kiện nào, chờ đợi bao nhiêu</t>
+        </is>
+      </c>
+      <c r="E89" s="20" t="inlineStr">
+        <is>
+          <t>eaa/diagnostics.py ManualMeasurement</t>
+        </is>
+      </c>
+      <c r="F89" s="20" t="inlineStr">
+        <is>
+          <t>TC-58c, TC-58d</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="20" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C90" s="20" t="inlineStr">
+        <is>
+          <t>Đo đặc tính thời gian thực, kể cả xấu nhất</t>
+        </is>
+      </c>
+      <c r="D90" s="20" t="inlineStr">
+        <is>
+          <t>Chu kỳ trung bình, chu kỳ DÀI NHẤT, dao động, tải CPU — ràng buộc áp lên trường hợp xấu nhất chứ không lên trung bình</t>
+        </is>
+      </c>
+      <c r="E90" s="20" t="inlineStr">
+        <is>
+          <t>projects/*/diagnostics/DS-06.c</t>
+        </is>
+      </c>
+      <c r="F90" s="20" t="inlineStr">
+        <is>
+          <t>TC-58b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C91" s="20" t="inlineStr">
+        <is>
+          <t>Kiểm độ bền dài hạn</t>
+        </is>
+      </c>
+      <c r="D91" s="20" t="inlineStr">
+        <is>
+          <t>Phát hiện reset qua bộ đếm thời gian chạy tụt; báo cáo không suy rộng quá quãng đã quan sát</t>
+        </is>
+      </c>
+      <c r="E91" s="20" t="inlineStr">
+        <is>
+          <t>eaa/endurance.py + eaa endurance</t>
+        </is>
+      </c>
+      <c r="F91" s="20" t="inlineStr">
+        <is>
+          <t>TC-58e..g</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="20" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C92" s="20" t="inlineStr">
+        <is>
+          <t>Chẩn đoán sự cố ngoài hiện trường</t>
+        </is>
+      </c>
+      <c r="D92" s="20" t="inlineStr">
+        <is>
+          <t>Dựng lại điều kiện trước khi đo; không tái hiện được thì nói CHƯA KẾT LUẬN ĐƯỢC thay vì đoán</t>
+        </is>
+      </c>
+      <c r="E92" s="20" t="inlineStr">
+        <is>
+          <t>eaa/diagnostics.py FieldCase</t>
+        </is>
+      </c>
+      <c r="F92" s="20" t="inlineStr">
+        <is>
+          <t>TC-59e, TC-59f</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="20" t="inlineStr">
+        <is>
+          <t>A. Khởi tạo &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C93" s="20" t="inlineStr">
+        <is>
+          <t>Agent đề xuất phạm vi, ràng buộc, tiêu chí, bảng chân</t>
+        </is>
+      </c>
+      <c r="D93" s="20" t="inlineStr">
+        <is>
+          <t>Bốn bản đề xuất của G0/G1; mỗi ràng buộc kèm HỆ QUẢ, mỗi tiêu chí là số + đơn vị + cách đo, mỗi chân được kiểm chức năng thay thế</t>
+        </is>
+      </c>
+      <c r="E93" s="20" t="inlineStr">
+        <is>
+          <t>eaa/propose.py</t>
+        </is>
+      </c>
+      <c r="F93" s="20" t="inlineStr">
+        <is>
+          <t>TC-54 (38 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="20" t="inlineStr">
+        <is>
+          <t>A. Khởi tạo &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C94" s="20" t="inlineStr">
+        <is>
+          <t>Danh sách tài liệu và trang cần trích, đích danh</t>
+        </is>
+      </c>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Suy từ hồ sơ phần cứng và đồ thị; chỉ xin phần CÒN THIẾU trích đoạn</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
+        <is>
+          <t>eaa/docplan.py</t>
+        </is>
+      </c>
+      <c r="F94" s="20" t="inlineStr">
+        <is>
+          <t>TC-55a..e</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="20" t="inlineStr">
+        <is>
+          <t>A. Khởi tạo &amp; phạm vi</t>
+        </is>
+      </c>
+      <c r="C95" s="20" t="inlineStr">
+        <is>
+          <t>Errata theo đúng rev silicon</t>
+        </is>
+      </c>
+      <c r="D95" s="20" t="inlineStr">
+        <is>
+          <t>'Chưa tra' khác hẳn 'chip sạch'; module chạm lỗi đã công bố được gọi tên</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
+        <is>
+          <t>eaa/docplan.py ErrataAnalysis</t>
+        </is>
+      </c>
+      <c r="F95" s="20" t="inlineStr">
+        <is>
+          <t>TC-55f..h</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="20" t="inlineStr">
+        <is>
+          <t>C. Tri thức &amp; RAG</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>Bộ chuẩn đánh giá truy xuất (golden set)</t>
+        </is>
+      </c>
+      <c r="D96" s="20" t="inlineStr">
+        <is>
+          <t>precision@3 trên bộ chuẩn của dự án, kèm chunk nhiễu có chủ ý</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
+        <is>
+          <t>eaa/goldenset.py + eaa report retrieval</t>
+        </is>
+      </c>
+      <c r="F96" s="20" t="inlineStr">
+        <is>
+          <t>TC-20 (10 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>C. Tri thức &amp; RAG</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="inlineStr">
+        <is>
+          <t>Ảnh màn hiện sóng thành số đo đề xuất</t>
+        </is>
+      </c>
+      <c r="D97" s="20" t="inlineStr">
+        <is>
+          <t>Kèm sai số đọc ảnh; người sửa được giá trị trước khi lưu, bản ghi giữ cả hai số</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
+        <is>
+          <t>eaa/ingest.py ScopeImageReader</t>
+        </is>
+      </c>
+      <c r="F97" s="20" t="inlineStr">
+        <is>
+          <t>TC-23 (10 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="20" t="inlineStr">
+        <is>
+          <t>D. Sinh mã</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Sinh giao diện TRƯỚC khi sinh thân</t>
+        </is>
+      </c>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Hợp đồng gọi trả lời ba câu chữ ký không nói được: ngắt / chặn / tái nhập</t>
+        </is>
+      </c>
+      <c r="E98" s="20" t="inlineStr">
+        <is>
+          <t>eaa/interfaces.py + khuôn của pack</t>
+        </is>
+      </c>
+      <c r="F98" s="20" t="inlineStr">
+        <is>
+          <t>TC-56a..e</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="20" t="inlineStr">
+        <is>
+          <t>D. Sinh mã</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="inlineStr">
+        <is>
+          <t>Ngân sách tài nguyên và token chia theo module</t>
+        </is>
+      </c>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Cảnh báo khi một module ăn quá phần; trần token tích lũy chặn TRƯỚC khi gọi mô hình</t>
+        </is>
+      </c>
+      <c r="E99" s="20" t="inlineStr">
+        <is>
+          <t>eaa/budget.py + eaa budget</t>
+        </is>
+      </c>
+      <c r="F99" s="20" t="inlineStr">
+        <is>
+          <t>TC-53 (30 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="20" t="inlineStr">
+        <is>
+          <t>E. Kiểm chứng &amp; cổng</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>Nêu đích danh phần KHÔNG kiểm được trên máy chủ</t>
+        </is>
+      </c>
+      <c r="D100" s="20" t="inlineStr">
+        <is>
+          <t>Thanh ghi, ngoại vi, ràng buộc thời gian — mỗi loại chỉ ra nơi nó được đóng</t>
+        </is>
+      </c>
+      <c r="E100" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/unittests.py host_gaps</t>
+        </is>
+      </c>
+      <c r="F100" s="20" t="inlineStr">
+        <is>
+          <t>TC-56f, TC-56g</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="20" t="inlineStr">
+        <is>
+          <t>E. Kiểm chứng &amp; cổng</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="inlineStr">
+        <is>
+          <t>Khoảng trống ngăn xếp ở tầm firmware</t>
+        </is>
+      </c>
+      <c r="D101" s="20" t="inlineStr">
+        <is>
+          <t>Số liệu SUY RA từ dung lượng trừ phần đã dùng; chỉ có nghĩa sau khi liên kết</t>
+        </is>
+      </c>
+      <c r="E101" s="20" t="inlineStr">
+        <is>
+          <t>eaa/budget.py derived</t>
+        </is>
+      </c>
+      <c r="F101" s="20" t="inlineStr">
+        <is>
+          <t>TC-53d</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>F. Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>Tiêm lỗi trong mô phỏng</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Bốn kiểu hỏng đặt tên theo hành vi; kiểm hệ có vào chế độ an toàn không</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>eaa/tools/sim_runner.py FaultSpec</t>
+        </is>
+      </c>
+      <c r="F102" s="20" t="inlineStr">
+        <is>
+          <t>TC-57a..e</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="20" t="inlineStr">
+        <is>
+          <t>F. Mô phỏng</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="inlineStr">
+        <is>
+          <t>Đề xuất mô hình đối tượng</t>
+        </is>
+      </c>
+      <c r="D103" s="20" t="inlineStr">
+        <is>
+          <t>Tham số chưa đo vào Assumption Log; mô hình BẮT BUỘC nêu hiện tượng nó bỏ qua</t>
+        </is>
+      </c>
+      <c r="E103" s="20" t="inlineStr">
+        <is>
+          <t>eaa/propose.py PlantModelProposal</t>
+        </is>
+      </c>
+      <c r="F103" s="20" t="inlineStr">
+        <is>
+          <t>TC-57f, TC-57g</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="20" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="20" t="inlineStr">
+        <is>
+          <t>K. Bàn giao &amp; vận hành</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>Tài liệu vận hành sinh từ dữ liệu dự án</t>
+        </is>
+      </c>
+      <c r="D104" s="20" t="inlineStr">
+        <is>
+          <t>Kèm mục 'điều hệ thống KHÔNG làm được', dựng từ chỗ hở thật chứ không viết tay</t>
+        </is>
+      </c>
+      <c r="E104" s="20" t="inlineStr">
+        <is>
+          <t>eaa/handover.py + eaa handover doc</t>
+        </is>
+      </c>
+      <c r="F104" s="20" t="inlineStr">
+        <is>
+          <t>TC-59a, TC-59b</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="20" t="inlineStr">
+        <is>
+          <t>K. Bàn giao &amp; vận hành</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="inlineStr">
+        <is>
+          <t>Đánh giá ảnh hưởng khi đổi linh kiện</t>
+        </is>
+      </c>
+      <c r="D105" s="20" t="inlineStr">
+        <is>
+          <t>So hai linh kiện rồi bắc cầu trên đồ thị ra module bị chạm</t>
+        </is>
+      </c>
+      <c r="E105" s="20" t="inlineStr">
+        <is>
+          <t>eaa/handover.py SwapAnalysis</t>
+        </is>
+      </c>
+      <c r="F105" s="20" t="inlineStr">
+        <is>
+          <t>TC-59c, TC-59d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="20" t="inlineStr">
+        <is>
+          <t>K. Bàn giao &amp; vận hành</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>Cập nhật thiết bị đã triển khai</t>
+        </is>
+      </c>
+      <c r="D106" s="20" t="inlineStr">
+        <is>
+          <t>Bậc đầu ĐÚNG MỘT thiết bị; phải có đường lui lấy từ known_good.lock</t>
+        </is>
+      </c>
+      <c r="E106" s="20" t="inlineStr">
+        <is>
+          <t>eaa/handover.py RolloutPlan</t>
+        </is>
+      </c>
+      <c r="F106" s="20" t="inlineStr">
+        <is>
+          <t>TC-59g, TC-59h</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="20" t="inlineStr">
+        <is>
+          <t>L. Siêu nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>Agent tự phát hiện sai lệch thiết kế</t>
+        </is>
+      </c>
+      <c r="D107" s="20" t="inlineStr">
+        <is>
+          <t>Đối chiếu module và lệnh với tài liệu; dựng nháp mục cho sổ sai lệch</t>
+        </is>
+      </c>
+      <c r="E107" s="20" t="inlineStr">
+        <is>
+          <t>eaa/deviation.py + eaa deviations</t>
+        </is>
+      </c>
+      <c r="F107" s="20" t="inlineStr">
+        <is>
+          <t>TC-60d..f</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="20" t="inlineStr">
+        <is>
+          <t>L. Siêu nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>Tự đánh giá quy trình</t>
+        </is>
+      </c>
+      <c r="D108" s="20" t="inlineStr">
+        <is>
+          <t>Chỉ ra cổng hay trượt nhất; mỗi đề xuất gắn với một con số quan sát được</t>
+        </is>
+      </c>
+      <c r="E108" s="20" t="inlineStr">
+        <is>
+          <t>eaa/kpi.py weak_points + eaa report review</t>
+        </is>
+      </c>
+      <c r="F108" s="20" t="inlineStr">
+        <is>
+          <t>TC-60g..i</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F85"/>
+  <autoFilter ref="A1:F108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3622,7 +4387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3671,17 +4436,17 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>B. Kiến trúc ba tầng</t>
+          <t>L. Siêu nghiệp vụ</t>
         </is>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>Thêm họ MCU mới không sửa engine (NFR-05)</t>
+          <t>Bộ từ vựng mức tin cậy dùng chung</t>
         </is>
       </c>
       <c r="D2" s="20" t="inlineStr">
         <is>
-          <t>Cấu trúc đã tách đúng, nhưng mới có duy nhất pack AVR</t>
+          <t>ĐÃ KIỂM / SUY RA / GIẢ ĐỊNH / KHÔNG KIỂM ĐƯỢC — một bộ cho toàn hệ</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
@@ -3691,7 +4456,7 @@
       </c>
       <c r="F2" s="20" t="inlineStr">
         <is>
-          <t>Chưa có pack thứ hai (STM32/ESP32) để chứng minh bằng thực nghiệm</t>
+          <t>Năm chỗ đã quy về bộ từ vựng chung; các đầu ra còn lại chưa gắn nhãn</t>
         </is>
       </c>
     </row>
@@ -3701,27 +4466,27 @@
       </c>
       <c r="B3" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Sinh firmware chẩn đoán từ mẫu</t>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
         </is>
       </c>
       <c r="D3" s="20" t="inlineStr">
         <is>
-          <t>Bộ khung ở pack + phần đo ở dự án, ghép bằng liên kết; eaa diagnose build</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
-        <is>
-          <t>Một phần</t>
+          <t>Tầng 2 của AIS §4.2</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
         </is>
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>2/6 kịch bản đã có phần đo (DS-01, DS-04); bốn kịch bản còn lại báo rõ 'chưa khai phần đo' thay vì im lặng</t>
+          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
         </is>
       </c>
     </row>
@@ -3731,17 +4496,17 @@
       </c>
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>C. Tri thức &amp; RAG</t>
+          <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+          <t>Cổng SIL cho mã C sinh ra</t>
         </is>
       </c>
       <c r="D4" s="20" t="inlineStr">
         <is>
-          <t>Tầng 2 của AIS §4.2</t>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
         </is>
       </c>
       <c r="E4" s="22" t="inlineStr">
@@ -3751,7 +4516,7 @@
       </c>
       <c r="F4" s="20" t="inlineStr">
         <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
@@ -3761,17 +4526,17 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
+          <t>I. Tương tác</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
         <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
+          <t>Giao diện hội thoại / TUI</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
         <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+          <t>Hiện là CLI từng lệnh rời</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -3781,7 +4546,7 @@
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
+          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
         </is>
       </c>
     </row>
@@ -3791,17 +4556,17 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>I. Tương tác</t>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>Giao diện hội thoại / TUI</t>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Hiện là CLI từng lệnh rời</t>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -3811,7 +4576,7 @@
       </c>
       <c r="F6" s="20" t="inlineStr">
         <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
@@ -3821,62 +4586,32 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
+          <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
+          <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
+          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Cố ý không làm</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>G. Công cụ &amp; môi trường</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>Tự cài KHÔNG hỏi người</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="inlineStr">
-        <is>
-          <t>Cố ý không làm</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Lộ trình mạch thật" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Đã làm được'!$A$1:$F$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Chưa làm được'!$A$1:$F$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -60,15 +60,15 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="002F5597"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -140,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,29 +165,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -196,7 +190,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -712,19 +706,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="8" t="n">
-        <v>1</v>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -859,22 +853,22 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="8" t="n">
-        <v>1</v>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -934,13 +928,13 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>0</v>
@@ -949,43 +943,43 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="B18" s="11" t="n">
+      <c r="B18" s="10" t="n">
+        <v>116</v>
+      </c>
+      <c r="C18" s="11" t="n">
         <v>113</v>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>107</v>
-      </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>0.9553571428571429</v>
+      <c r="G18" s="12" t="n">
+        <v>0.9826086956521739</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Số liệu nền</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Test tự động đang xanh</t>
         </is>
@@ -997,7 +991,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Dòng mã engine (eaa/)</t>
         </is>
@@ -1009,7 +1003,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Lệnh CLI</t>
         </is>
@@ -1021,7 +1015,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Platform Pack</t>
         </is>
@@ -1033,7 +1027,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Mô hình nền</t>
         </is>
@@ -1045,7 +1039,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Sai lệch thiết kế đã ghi</t>
         </is>
@@ -1057,14 +1051,14 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Ý nghĩa bốn trạng thái</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>Đã làm</t>
         </is>
@@ -1076,7 +1070,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Một phần</t>
         </is>
@@ -1088,7 +1082,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
@@ -1100,7 +1094,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Cố ý không làm</t>
         </is>
@@ -1122,7 +1116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1166,3217 +1160,3397 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>A. Khung &amp; trạng thái</t>
         </is>
       </c>
-      <c r="C2" s="20" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>Project State ghi nguyên tử</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>Ghi tạm → fsync → os.replace → fsync thư mục; sống sót qua crash giữa chừng</t>
         </is>
       </c>
-      <c r="E2" s="20" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>eaa/state.py</t>
         </is>
       </c>
-      <c r="F2" s="20" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>TC-03 (24 test)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n">
+      <c r="A3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>A. Khung &amp; trạng thái</t>
         </is>
       </c>
-      <c r="C3" s="20" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>Khóa liên tiến trình</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Khóa tái nhập, tự thu hồi khóa mồ côi khi tiến trình giữ khóa đã chết</t>
         </is>
       </c>
-      <c r="E3" s="20" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>eaa/state.py</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>TC-03</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A. Khung &amp; trạng thái</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Máy trạng thái 13 công đoạn</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>A1..F1, mỗi cung chuyển khai báo gate phải qua; không có cung tắt</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>eaa/policy.py</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>TC-08 (58 test)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>A. Khung &amp; trạng thái</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Bảng phân quyền AUTO / HUMAN</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Pha nào máy tự đi, pha nào bắt buộc có người</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>eaa/policy.py</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>TC-08</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>A. Khung &amp; trạng thái</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Khôi phục phiên sau khi tắt máy</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Đọc lại Project State và nói bước kế tiếp</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>eaa resume / status</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>test_cli_s0.py</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>B. Kiến trúc ba tầng</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Engine sạch phần cứng</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Không một hằng số, tên thanh ghi hay tên chip nào trong eaa/</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>toàn bộ eaa/</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>TC-38 quét mỗi commit</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>B. Kiến trúc ba tầng</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Platform Pack qua interface</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Engine gọi toolchain chỉ qua eaa/platform.py; pack khai báo năng lực bằng YAML</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>eaa/platform.py</t>
         </is>
       </c>
-      <c r="F8" s="20" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>test_platform_pack.py</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>B. Kiến trúc ba tầng</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Thêm họ MCU mới không sửa engine (NFR-05)</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Pack thứ hai (STM32 Cortex-M4F) thêm vào KHÔNG sinh một nhánh rẽ nào trong eaa/</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>packs/avr/ + packs/stm32/</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>TC-47</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Kho ràng buộc + hồ sơ phần cứng + thư viện prompt</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>constraints.yaml, hardware_profile.yaml, prompt nền tảng theo pack</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>eaa/kb.py</t>
         </is>
       </c>
-      <c r="F10" s="20" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>test_kb.py</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Knowledge Graph module→ngoại vi→thanh ghi→chunk</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Đồ thị tự dựng từ kho tri thức; khớp tên thanh ghi chính xác, không nhúng vector</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>eaa/graph.py</t>
         </is>
       </c>
-      <c r="F11" s="20" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>TC-18 (31 test)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Truy xuất chunk tất định</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Cùng câu hỏi cho cùng top-k; không phụ thuộc thứ tự ngẫu nhiên</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>eaa/graph.py</t>
         </is>
       </c>
-      <c r="F12" s="20" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>TC-18</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Nén ngữ cảnh K1–K7, ngân sách 8.000 token</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>7 tầng có ngân sách con; cắt luật lỗi rồi tới interface, KHÔNG BAO GIỜ cắt chunk</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="19" t="inlineStr">
         <is>
           <t>eaa/composer.py</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>TC-04 (36 test), TC-16</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Bắt buộc trích dẫn // ref: &lt;chunk-id&gt;</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Mã cấu hình thanh ghi không có trích dẫn thì cổng static chặn</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/static.py</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>TC-17</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Append-only + supersede + stale set</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Không ghi đè vật lý; chunk bị thay thì mã dùng nó bị đánh dấu cần xem lại</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>eaa/lifecycle.py</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F15" s="19" t="inlineStr">
         <is>
           <t>TC-29 (23 test)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Ba đường truy vấn ngược</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Từ chunk tìm ra mã: qua đồ thị, qua // ref:, qua trailer chunk-ids của commit</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>eaa/lifecycle.py</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>TC-29</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Nạp PDF thành proposed fact</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Trích đoạn luôn ở trạng thái 'proposed', phải qua G2 mới thành tri thức</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>eaa/ingest.py</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>TC-22 (44 test)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Nguồn web giới hạn miền nhà sản xuất</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>So theo hậu tố tên miền, không so chuỗi con</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>eaa/ingest.py</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>TC-22</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Sổ giả định (Assumption Log)</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Giả định được ghi, và bị thay khi có số đo thật</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>eaa/ingest.py</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>TC-22</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Tự đánh giá đủ thông tin (RIC)</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>Trả về CÓ / THIẾU / MÂU THUẪN; chuẩn hóa số nên 0b00 == 0x00 == 0</t>
         </is>
       </c>
-      <c r="E20" s="20" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>eaa/readiness.py</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>TC-24 (18 test)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="n">
+      <c r="A21" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>C. Tri thức &amp; RAG</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>Tầng 2 của AIS §4.2: quan hệ trước, BM25 lấp chỗ trống, ngưỡng là ĐỘ PHỦ từ khóa</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>eaa/rag.py</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>TC-64 (20 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Vòng lặp chuẩn 13 bước</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>Từ chọn module tới merge, mỗi bước ghi vết vào Project State</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>eaa/orchestrator.py</t>
         </is>
       </c>
-      <c r="F21" s="20" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>TC-06 (28 test)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Vòng tự sửa ≤ 3 lần, dạng patch</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Gửi patch chứ không gửi lại cả tệp; quá 3 lần thì dừng và bàn giao người</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>eaa/orchestrator.py</t>
         </is>
       </c>
-      <c r="F22" s="20" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>TC-06, TC-19</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Kiểm ngân sách token TRƯỚC khi gọi mô hình</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
         <is>
           <t>count_tokens chạy trước; vượt ngân sách thì không gọi API</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/base.py</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>TC-16</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Adapter Gemini Pro 3.1 ghim phiên bản</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D25" s="19" t="inlineStr">
         <is>
           <t>REST thuần bằng urllib, stateless mỗi lần gọi, clamp output limit theo model thật</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/gemini.py</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>TC-11 (31 test)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Lối gọi văn xuôi complete()</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>Tra cứu / phân loại lỗi không phải sinh mã, nên không bị đòi khối ```file:</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/*.py</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>TC-39</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>MockLLM tất định cho Sprint 1–3</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Cùng interface với mô hình thật; kiểm thử tích hợp không tốn API</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/mock.py</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>toàn bộ test tích hợp</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Nhật ký lời gọi + phát lại</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D28" s="19" t="inlineStr">
         <is>
           <t>Lưu (băm prompt → phản hồi) làm bằng chứng; ReplayClient chạy lại không tốn API</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr">
+      <c r="E28" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/calllog.py</t>
         </is>
       </c>
-      <c r="F27" s="20" t="inlineStr">
+      <c r="F28" s="19" t="inlineStr">
         <is>
           <t>TC-15</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Phát hiện mô hình trôi hành vi</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Cùng băm prompt mà hai phản hồi khác nhau thì hiện ra</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E29" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/calllog.py</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>TC-15</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="20" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Che khóa API ở mọi lối ra</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D30" s="19" t="inlineStr">
         <is>
           <t>Không vào log, commit, repr, thông báo lỗi hay băm prompt</t>
         </is>
       </c>
-      <c r="E29" s="20" t="inlineStr">
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>eaa/llm/base.py</t>
         </is>
       </c>
-      <c r="F29" s="20" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>TC-14</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Ráp firmware hoàn chỉnh (main + scheduler)</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Sinh vòng lặp chính từ khuôn của pack, dịch mọi module đã merge, liên kết, ra ảnh nạp được</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr">
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py + eaa build</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F31" s="19" t="inlineStr">
         <is>
           <t>TC-41 (24 test)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="19" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Bộ định thời hợp tác</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Bảng việc định kỳ; ngắt chỉ tăng bộ đếm, đọc bộ đếm trong khối nguyên tử</t>
         </is>
       </c>
-      <c r="E31" s="20" t="inlineStr">
+      <c r="E32" s="19" t="inlineStr">
         <is>
           <t>packs/avr/templates/main.c.tmpl</t>
         </is>
       </c>
-      <c r="F31" s="20" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>TC-41</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="20" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="19" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Module đã merge không được bỏ quên khi ráp</t>
         </is>
       </c>
-      <c r="D32" s="20" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Merge mà vắng mặt trong firmware.yaml là LỖI; không chạy định kỳ thì khai step: null</t>
         </is>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py</t>
         </is>
       </c>
-      <c r="F32" s="20" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>TC-41b</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="20" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="19" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>Mã chưa merge không vào được firmware</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Bản thiết kế ráp nhắc tới module chưa qua G3 thì dừng</t>
         </is>
       </c>
-      <c r="E33" s="20" t="inlineStr">
+      <c r="E34" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py</t>
         </is>
       </c>
-      <c r="F33" s="20" t="inlineStr">
+      <c r="F34" s="19" t="inlineStr">
         <is>
           <t>TC-41c</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="19" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Bốn cổng công cụ</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
         <is>
           <t>compile, static, unittests, size — mỗi cổng trả ToolReport có bằng chứng</t>
         </is>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E35" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
+      <c r="F35" s="19" t="inlineStr">
         <is>
           <t>TC-07 (43 test)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Bất biến merge</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Chỉ merge khi TOÀN BỘ ToolReport.passed VÀ G3 duyệt; không có nhánh thứ hai</t>
         </is>
       </c>
-      <c r="E35" s="20" t="inlineStr">
+      <c r="E36" s="19" t="inlineStr">
         <is>
           <t>eaa/vcs.py + orchestrator</t>
         </is>
       </c>
-      <c r="F35" s="20" t="inlineStr">
+      <c r="F36" s="19" t="inlineStr">
         <is>
           <t>TC-01 (45 test)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="20" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Băm nội dung xuyên suốt</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Hồ sơ gate → quyết định → ủy quyền merge cùng một băm: người duyệt X thì merge đúng X</t>
         </is>
       </c>
-      <c r="E36" s="20" t="inlineStr">
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>eaa/gates.py, eaa/vcs.py</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F37" s="19" t="inlineStr">
         <is>
           <t>TC-01</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="20" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="19" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>5 Human Gate không vượt được</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Không có cờ --yes / --force / --skip-gate nào tồn tại trong CLI</t>
         </is>
       </c>
-      <c r="E37" s="20" t="inlineStr">
+      <c r="E38" s="19" t="inlineStr">
         <is>
           <t>eaa/gates.py</t>
         </is>
       </c>
-      <c r="F37" s="20" t="inlineStr">
+      <c r="F38" s="19" t="inlineStr">
         <is>
           <t>TC-01, TC-28, TC-34</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="20" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="19" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Phiên không có người ≠ người đồng ý</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Không phải TTY thì ném GateNotInteractive chứ không mặc định duyệt</t>
         </is>
       </c>
-      <c r="E38" s="20" t="inlineStr">
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>eaa/gates.py</t>
         </is>
       </c>
-      <c r="F38" s="20" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>TC-28</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Lỗi cấu hình không đi vào vòng tự sửa</t>
         </is>
       </c>
-      <c r="D39" s="20" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Thiếu luật, thiếu công cụ → chặn ngay, không đốt 3 lượt sửa vô ích</t>
         </is>
       </c>
-      <c r="E39" s="20" t="inlineStr">
+      <c r="E40" s="19" t="inlineStr">
         <is>
           <t>eaa/orchestrator.py</t>
         </is>
       </c>
-      <c r="F39" s="20" t="inlineStr">
+      <c r="F40" s="19" t="inlineStr">
         <is>
           <t>TC-06</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="20" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="20" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="19" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C40" s="20" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Sổ lỗi ảo giác</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Append-only; phân xử ghi thành sự kiện mới chứ không sửa sự kiện cũ</t>
         </is>
       </c>
-      <c r="E40" s="20" t="inlineStr">
+      <c r="E41" s="19" t="inlineStr">
         <is>
           <t>eaa/ledger.py</t>
         </is>
       </c>
-      <c r="F40" s="20" t="inlineStr">
+      <c r="F41" s="19" t="inlineStr">
         <is>
           <t>TC-10 (20 test)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="20" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="20" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="19" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Báo cáo KPI</t>
         </is>
       </c>
-      <c r="D41" s="20" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>Tỉ lệ qua cổng, số lượt tự sửa, token tiêu thụ theo module</t>
         </is>
       </c>
-      <c r="E41" s="20" t="inlineStr">
+      <c r="E42" s="19" t="inlineStr">
         <is>
           <t>eaa/kpi.py + eaa report</t>
         </is>
       </c>
-      <c r="F41" s="20" t="inlineStr">
+      <c r="F42" s="19" t="inlineStr">
         <is>
           <t>TC-09</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="20" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>F. Mô phỏng</t>
         </is>
       </c>
-      <c r="C42" s="20" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Mô hình con lắc ngược + MIL</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D43" s="19" t="inlineStr">
         <is>
           <t>Mô phỏng động lực học, đánh giá theo tiêu chí nghiệm thu</t>
         </is>
       </c>
-      <c r="E42" s="20" t="inlineStr">
+      <c r="E43" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/sim.py, sim_runner.py</t>
         </is>
       </c>
-      <c r="F42" s="20" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>TC-12 (12 test)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="20" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>F. Mô phỏng</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Quét tham số</t>
         </is>
       </c>
-      <c r="D43" s="20" t="inlineStr">
+      <c r="D44" s="19" t="inlineStr">
         <is>
           <t>Quét lưới bộ tham số điều khiển, xếp hạng theo chỉ số</t>
         </is>
       </c>
-      <c r="E43" s="20" t="inlineStr">
+      <c r="E44" s="19" t="inlineStr">
         <is>
           <t>eaa sim --sweep</t>
         </is>
       </c>
-      <c r="F43" s="20" t="inlineStr">
+      <c r="F44" s="19" t="inlineStr">
         <is>
           <t>TC-12</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>F. Mô phỏng</t>
         </is>
       </c>
-      <c r="C44" s="20" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Chỉ số thời gian ổn định đo đúng</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Đo từ lần cuối tín hiệu rời dải, tính từ lúc nhiễu kết thúc</t>
         </is>
       </c>
-      <c r="E44" s="20" t="inlineStr">
+      <c r="E45" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/sim.py</t>
         </is>
       </c>
-      <c r="F44" s="20" t="inlineStr">
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>test_sim_verification.py</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="20" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C45" s="20" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>Chế độ 1 — quét công cụ đã có</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D46" s="19" t="inlineStr">
         <is>
           <t>Có gì trên máy, phiên bản bao nhiêu, thiếu thì chặn cổng nào</t>
         </is>
       </c>
-      <c r="E45" s="20" t="inlineStr">
+      <c r="E46" s="19" t="inlineStr">
         <is>
           <t>eaa doctor</t>
         </is>
       </c>
-      <c r="F45" s="20" t="inlineStr">
+      <c r="F46" s="19" t="inlineStr">
         <is>
           <t>TC-34 (37 test)</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="20" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Chế độ 2 — sinh lệnh cài</t>
         </is>
       </c>
-      <c r="D46" s="20" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>Sinh đúng lệnh theo hệ điều hành, hỏi người trước từng lệnh</t>
         </is>
       </c>
-      <c r="E46" s="20" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>eaa doctor --fix</t>
         </is>
       </c>
-      <c r="F46" s="20" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>TC-34, TC-37</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="19" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Chế độ 3 — TỰ TÌM công cụ chưa biết</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D48" s="19" t="inlineStr">
         <is>
           <t>Phát hiện → tra cứu bằng mô hình → đề xuất; đây là phần vừa làm xong</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E48" s="19" t="inlineStr">
         <is>
           <t>eaa/toolsearch.py</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>TC-39 (29 test)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Nhu cầu công cụ suy từ Platform Pack</t>
         </is>
       </c>
-      <c r="D48" s="20" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Không chép tay danh sách: pack.yaml đã ghi mọi chương trình nó gọi</t>
         </is>
       </c>
-      <c r="E48" s="20" t="inlineStr">
+      <c r="E49" s="19" t="inlineStr">
         <is>
           <t>eaa/toolsearch.py</t>
         </is>
       </c>
-      <c r="F48" s="20" t="inlineStr">
+      <c r="F49" s="19" t="inlineStr">
         <is>
           <t>TC-39</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="20" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="19" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>Kiểm nguồn cài trước khi tới tay người</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>10 trình quản lý gói chính thống; tải trực tiếp phải HTTPS + miền cho phép + sha256</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E50" s="19" t="inlineStr">
         <is>
           <t>eaa/toolsearch.py</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>TC-39</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="20" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="19" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>Đề xuất công cụ vào manifest qua G2</t>
         </is>
       </c>
-      <c r="D50" s="20" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Append + supersede, mang theo approved_by / approved_at</t>
         </is>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E51" s="19" t="inlineStr">
         <is>
           <t>eaa gate approve G2</t>
         </is>
       </c>
-      <c r="F50" s="20" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>TC-39</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="20" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="19" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>Ràng buộc phiên bản của pack đè lên đề xuất</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>pack.yaml ghi avr-gcc &gt;=12.0, mô hình đề xuất 7.3 — lấy theo pack</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E52" s="19" t="inlineStr">
         <is>
           <t>eaa/toolsearch.py</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
+      <c r="F52" s="19" t="inlineStr">
         <is>
           <t>TC-39</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="20" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="20" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>Khóa môi trường + cảnh báo trôi</t>
         </is>
       </c>
-      <c r="D52" s="20" t="inlineStr">
+      <c r="D53" s="19" t="inlineStr">
         <is>
           <t>env_lock.json; toolchain đổi phiên bản thì cảnh báo trước khi so sánh A/B</t>
         </is>
       </c>
-      <c r="E52" s="20" t="inlineStr">
+      <c r="E53" s="19" t="inlineStr">
         <is>
           <t>eaa/doctor.py</t>
         </is>
       </c>
-      <c r="F52" s="20" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>TC-36</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="20" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="19" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>Thẻ công cụ</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D54" s="19" t="inlineStr">
         <is>
           <t>Cú pháp gọi, cách đọc dòng lỗi, phiên bản đã xác nhận</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E54" s="19" t="inlineStr">
         <is>
           <t>eaa/doctor.py</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F54" s="19" t="inlineStr">
         <is>
           <t>TC-37</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="20" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="19" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>Tự phát hiện cổng USB / thiết bị cắm vào</t>
         </is>
       </c>
-      <c r="D54" s="20" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Liệt kê cổng nối tiếp, khớp VID/PID với bo dự án khai; không đọc được thì nói thẳng</t>
         </is>
       </c>
-      <c r="E54" s="20" t="inlineStr">
+      <c r="E55" s="19" t="inlineStr">
         <is>
           <t>eaa/serialport.py + eaa ports</t>
         </is>
       </c>
-      <c r="F54" s="20" t="inlineStr">
+      <c r="F55" s="19" t="inlineStr">
         <is>
           <t>TC-42a (8 test)</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="20" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="20" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="19" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>H. Phiên bản mã</t>
         </is>
       </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>Ba hạng chất lượng</t>
         </is>
       </c>
-      <c r="D55" s="20" t="inlineStr">
+      <c r="D56" s="19" t="inlineStr">
         <is>
           <t>build-ok &lt; sim-verified &lt; hw-verified; hạng cao đòi bằng chứng tương ứng</t>
         </is>
       </c>
-      <c r="E55" s="20" t="inlineStr">
+      <c r="E56" s="19" t="inlineStr">
         <is>
           <t>eaa/versions.py</t>
         </is>
       </c>
-      <c r="F55" s="20" t="inlineStr">
+      <c r="F56" s="19" t="inlineStr">
         <is>
           <t>TC-30 (26 test)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="20" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="20" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>H. Phiên bản mã</t>
         </is>
       </c>
-      <c r="C56" s="20" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>known_good.lock chỉ cập nhật tại G4</t>
         </is>
       </c>
-      <c r="D56" s="20" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Phong hạng hw-verified đòi quyết định G4 VÀ số đo thật</t>
         </is>
       </c>
-      <c r="E56" s="20" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
         <is>
           <t>eaa/versions.py</t>
         </is>
       </c>
-      <c r="F56" s="20" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>TC-30</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="20" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="19" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>H. Phiên bản mã</t>
         </is>
       </c>
-      <c r="C57" s="20" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>Quay lui về bản known-good</t>
         </is>
       </c>
-      <c r="D57" s="20" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>Rollback không làm mất bản known-good đang giữ</t>
         </is>
       </c>
-      <c r="E57" s="20" t="inlineStr">
+      <c r="E58" s="19" t="inlineStr">
         <is>
           <t>eaa rollback</t>
         </is>
       </c>
-      <c r="F57" s="20" t="inlineStr">
+      <c r="F58" s="19" t="inlineStr">
         <is>
           <t>TC-30</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="20" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="19" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>H. Phiên bản mã</t>
         </is>
       </c>
-      <c r="C58" s="20" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>Commit truy vết đầy đủ (NFR-07)</t>
         </is>
       </c>
-      <c r="D58" s="20" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Mỗi commit mang băm prompt, model, phiên bản ràng buộc, danh sách chunk</t>
         </is>
       </c>
-      <c r="E58" s="20" t="inlineStr">
+      <c r="E59" s="19" t="inlineStr">
         <is>
           <t>eaa/vcs.py</t>
         </is>
       </c>
-      <c r="F58" s="20" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>TC-01</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="19" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>H. Phiên bản mã</t>
         </is>
       </c>
-      <c r="C59" s="20" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>Kho phẩm xuất</t>
         </is>
       </c>
-      <c r="D59" s="20" t="inlineStr">
+      <c r="D60" s="19" t="inlineStr">
         <is>
           <t>list / get / regen; gửi lại có kiểm băm để biết bản gửi có bị đổi không</t>
         </is>
       </c>
-      <c r="E59" s="20" t="inlineStr">
+      <c r="E60" s="19" t="inlineStr">
         <is>
           <t>eaa docs</t>
         </is>
       </c>
-      <c r="F59" s="20" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>TC-32 (33 test)</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="20" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="20" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C60" s="20" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>17 lệnh CLI phủ 10 use case</t>
         </is>
       </c>
-      <c r="D60" s="20" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>init, plan, gen, gate, sim, doctor, docs, tune, rollback, diagnose...</t>
         </is>
       </c>
-      <c r="E60" s="20" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>eaa/cli.py</t>
         </is>
       </c>
-      <c r="F60" s="20" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>test_cli_e2e.py</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="20" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="20" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="19" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C61" s="20" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>Hồ sơ gate đủ để quyết định</t>
         </is>
       </c>
-      <c r="D61" s="20" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Tóm tắt + chi tiết + băm nội dung; G4 nêu tiêu chí trước, số đo sau</t>
         </is>
       </c>
-      <c r="E61" s="20" t="inlineStr">
+      <c r="E62" s="19" t="inlineStr">
         <is>
           <t>eaa/gates.py</t>
         </is>
       </c>
-      <c r="F61" s="20" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>TC-01, TC-28</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="20" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="20" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="19" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C62" s="20" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>Từ chối phải có lý do</t>
         </is>
       </c>
-      <c r="D62" s="20" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
         <is>
           <t>GateDecision đòi tên người, và đòi lý do khi từ chối</t>
         </is>
       </c>
-      <c r="E62" s="20" t="inlineStr">
+      <c r="E63" s="19" t="inlineStr">
         <is>
           <t>eaa/gates.py</t>
         </is>
       </c>
-      <c r="F62" s="20" t="inlineStr">
+      <c r="F63" s="19" t="inlineStr">
         <is>
           <t>TC-28</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="20" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="20" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="19" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C63" s="20" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>Trình NHIỀU phương án để người chọn</t>
         </is>
       </c>
-      <c r="D63" s="20" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>eaa decide dựng tập phương án; gate đòi --option, không lấy gợi ý làm mặc định</t>
         </is>
       </c>
-      <c r="E63" s="20" t="inlineStr">
+      <c r="E64" s="19" t="inlineStr">
         <is>
           <t>eaa/options.py + eaa decide</t>
         </is>
       </c>
-      <c r="F63" s="20" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>TC-46 (32 test)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="20" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="19" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C64" s="20" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>Mỗi phương án phải nói mặt trái</t>
         </is>
       </c>
-      <c r="D64" s="20" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Thiếu cons là lỗi — danh sách toàn ưu điểm chỉ chuyển trách nhiệm sang người bấm</t>
         </is>
       </c>
-      <c r="E64" s="20" t="inlineStr">
+      <c r="E65" s="19" t="inlineStr">
         <is>
           <t>eaa/options.py</t>
         </is>
       </c>
-      <c r="F64" s="20" t="inlineStr">
+      <c r="F65" s="19" t="inlineStr">
         <is>
           <t>TC-46b</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="20" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="20" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="19" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C65" s="20" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>Agent tự giải thích 'vì sao chọn cách này'</t>
         </is>
       </c>
-      <c r="D65" s="20" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Mỗi phương án kèm rationale; gợi ý có lý do nhưng không thay quyết định</t>
         </is>
       </c>
-      <c r="E65" s="20" t="inlineStr">
+      <c r="E66" s="19" t="inlineStr">
         <is>
           <t>eaa/options.py</t>
         </is>
       </c>
-      <c r="F65" s="20" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>TC-46</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="20" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="20" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="19" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>I. Tương tác</t>
         </is>
       </c>
-      <c r="C66" s="20" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>Phương án bị loại vẫn tra lại được</t>
         </is>
       </c>
-      <c r="D66" s="20" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Quyết định mang cả tập, kể cả cái bị loại; từ chối cả tập cũng được lưu</t>
         </is>
       </c>
-      <c r="E66" s="20" t="inlineStr">
+      <c r="E67" s="19" t="inlineStr">
         <is>
           <t>eaa/gates.py</t>
         </is>
       </c>
-      <c r="F66" s="20" t="inlineStr">
+      <c r="F67" s="19" t="inlineStr">
         <is>
           <t>TC-46d</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="20" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>I. Tương tác</t>
+        </is>
+      </c>
+      <c r="C68" s="19" t="inlineStr">
+        <is>
+          <t>Giao diện hội thoại</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Nói bằng tiếng Việt; Agent tự chọn và chạy lệnh, đọc kết quả, lặp, rồi trả lời</t>
+        </is>
+      </c>
+      <c r="E68" s="19" t="inlineStr">
+        <is>
+          <t>eaa/agent.py + eaa chat</t>
+        </is>
+      </c>
+      <c r="F68" s="19" t="inlineStr">
+        <is>
+          <t>TC-61 (39 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="19" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>I. Tương tác</t>
+        </is>
+      </c>
+      <c r="C69" s="19" t="inlineStr">
+        <is>
+          <t>Gate và phần cứng ngoài tầm với của vòng hội thoại</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Danh mục công cụ KHÔNG chứa gate approve, flash, doctor --fix, tune, gen — chặn bằng cấu tạo, không bằng lời dặn trong prompt</t>
+        </is>
+      </c>
+      <c r="E69" s="19" t="inlineStr">
+        <is>
+          <t>eaa/agent.py TOOLBOX</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="inlineStr">
+        <is>
+          <t>TC-61b, TC-61c</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="19" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>I. Tương tác</t>
+        </is>
+      </c>
+      <c r="C70" s="19" t="inlineStr">
+        <is>
+          <t>Hiểu ngữ nghĩa khi khớp từ khóa trượt</t>
+        </is>
+      </c>
+      <c r="D70" s="19" t="inlineStr">
+        <is>
+          <t>Bậc 2 dùng mô hình cho chọn kịch bản và truy hồi phẩm xuất; kết quả đánh dấu PHỎNG ĐOÁN</t>
+        </is>
+      </c>
+      <c r="E70" s="19" t="inlineStr">
+        <is>
+          <t>diagnostics.select_smart, registry.find_smart</t>
+        </is>
+      </c>
+      <c r="F70" s="19" t="inlineStr">
+        <is>
+          <t>TC-62 (19 test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C67" s="20" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>Chẩn đoán hai kênh</t>
         </is>
       </c>
-      <c r="D67" s="20" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Giao của telemetry máy và quan sát người; thiếu một kênh thì TỪ CHỐI kết luận</t>
         </is>
       </c>
-      <c r="E67" s="20" t="inlineStr">
+      <c r="E71" s="19" t="inlineStr">
         <is>
           <t>eaa/diagnostics.py</t>
         </is>
       </c>
-      <c r="F67" s="20" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>TC-27 (33 test)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="20" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="19" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C68" s="20" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>Bộ kịch bản chẩn đoán DS-01..06</t>
         </is>
       </c>
-      <c r="D68" s="20" t="inlineStr">
+      <c r="D72" s="19" t="inlineStr">
         <is>
           <t>Khai báo bằng YAML ở tầng dự án, engine không biết nội dung</t>
         </is>
       </c>
-      <c r="E68" s="20" t="inlineStr">
+      <c r="E72" s="19" t="inlineStr">
         <is>
           <t>projects/*/diagnostics.yaml</t>
         </is>
       </c>
-      <c r="F68" s="20" t="inlineStr">
+      <c r="F72" s="19" t="inlineStr">
         <is>
           <t>TC-27</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="20" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="20" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="19" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C69" s="20" t="inlineStr">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>Checklist an toàn trước kịch bản gây chuyển động</t>
         </is>
       </c>
-      <c r="D69" s="20" t="inlineStr">
+      <c r="D73" s="19" t="inlineStr">
         <is>
           <t>Kịch bản làm mạch chuyển động đòi xác nhận đủ checklist</t>
         </is>
       </c>
-      <c r="E69" s="20" t="inlineStr">
+      <c r="E73" s="19" t="inlineStr">
         <is>
           <t>eaa/diagnostics.py</t>
         </is>
       </c>
-      <c r="F69" s="20" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>TC-27</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="20" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="20" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="19" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C70" s="20" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>Biên dịch từng module rồi liên kết riêng</t>
         </is>
       </c>
-      <c r="D70" s="20" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>compile dùng -c sinh tệp đối tượng; link và hex là hai năng lực riêng của pack</t>
         </is>
       </c>
-      <c r="E70" s="20" t="inlineStr">
+      <c r="E74" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/compile.py, packs/avr/pack.yaml</t>
         </is>
       </c>
-      <c r="F70" s="20" t="inlineStr">
+      <c r="F74" s="19" t="inlineStr">
         <is>
           <t>TC-40 (19 test)</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="20" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="20" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="19" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C71" s="20" t="inlineStr">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>Ráp ảnh nạp được (.elf → .hex)</t>
         </is>
       </c>
-      <c r="D71" s="20" t="inlineStr">
+      <c r="D75" s="19" t="inlineStr">
         <is>
           <t>LinkGate gộp tệp đối tượng thành ELF rồi đổi sang định dạng nạp được</t>
         </is>
       </c>
-      <c r="E71" s="20" t="inlineStr">
+      <c r="E75" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/compile.py</t>
         </is>
       </c>
-      <c r="F71" s="20" t="inlineStr">
+      <c r="F75" s="19" t="inlineStr">
         <is>
           <t>TC-40c</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="20" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="20" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C72" s="20" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>Đo kích thước nói rõ đang đo tầm nào</t>
         </is>
       </c>
-      <c r="D72" s="20" t="inlineStr">
+      <c r="D76" s="19" t="inlineStr">
         <is>
           <t>size_scope phân biệt chiếm dụng của một module lẻ với của cả firmware</t>
         </is>
       </c>
-      <c r="E72" s="20" t="inlineStr">
+      <c r="E76" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/compile.py</t>
         </is>
       </c>
-      <c r="F72" s="20" t="inlineStr">
+      <c r="F76" s="19" t="inlineStr">
         <is>
           <t>TC-40d</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="20" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="20" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="19" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C73" s="20" t="inlineStr">
+      <c r="C77" s="19" t="inlineStr">
         <is>
           <t>Ngưỡng bộ nhớ đo trên CẢ firmware</t>
         </is>
       </c>
-      <c r="D73" s="20" t="inlineStr">
+      <c r="D77" s="19" t="inlineStr">
         <is>
           <t>flash_pct_max lần đầu áp lên thứ sẽ nạp xuống mạch, không lên module lẻ</t>
         </is>
       </c>
-      <c r="E73" s="20" t="inlineStr">
+      <c r="E77" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py</t>
         </is>
       </c>
-      <c r="F73" s="20" t="inlineStr">
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>TC-41e</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="20" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="20" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="19" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C74" s="20" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>Nạp firmware xuống mạch qua USB</t>
         </is>
       </c>
-      <c r="D74" s="20" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
         <is>
           <t>eaa flash gọi năng lực flash của pack; bốn phép kiểm rồi mới hỏi người</t>
         </is>
       </c>
-      <c r="E74" s="20" t="inlineStr">
+      <c r="E78" s="19" t="inlineStr">
         <is>
           <t>eaa/flash.py + eaa flash</t>
         </is>
       </c>
-      <c r="F74" s="20" t="inlineStr">
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>TC-42 (30 test)</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="20" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="20" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C75" s="20" t="inlineStr">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>Bốn phép kiểm trước khi nạp</t>
         </is>
       </c>
-      <c r="D75" s="20" t="inlineStr">
+      <c r="D79" s="19" t="inlineStr">
         <is>
           <t>Có ảnh · kho mã sạch · ảnh mới hơn nguồn · người xác nhận — đều là 'không', không phải cảnh báo</t>
         </is>
       </c>
-      <c r="E75" s="20" t="inlineStr">
+      <c r="E79" s="19" t="inlineStr">
         <is>
           <t>eaa/flash.py</t>
         </is>
       </c>
-      <c r="F75" s="20" t="inlineStr">
+      <c r="F79" s="19" t="inlineStr">
         <is>
           <t>TC-42b, TC-42c</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="20" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="20" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="19" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C76" s="20" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>Nhật ký nạp append-only</t>
         </is>
       </c>
-      <c r="D76" s="20" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
         <is>
           <t>Commit nào, ảnh nào (kèm băm), cổng nào, ai, lúc nào — ghi cả lần trượt</t>
         </is>
       </c>
-      <c r="E76" s="20" t="inlineStr">
+      <c r="E80" s="19" t="inlineStr">
         <is>
           <t>eaa flash --history</t>
         </is>
       </c>
-      <c r="F76" s="20" t="inlineStr">
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>TC-42d</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="20" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="20" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="19" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C77" s="20" t="inlineStr">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>Engine không đoán cổng để nạp</t>
         </is>
       </c>
-      <c r="D77" s="20" t="inlineStr">
+      <c r="D81" s="19" t="inlineStr">
         <is>
           <t>Nhận ra đúng một cổng thì tự chọn; mơ hồ thì dừng và đòi --port</t>
         </is>
       </c>
-      <c r="E77" s="20" t="inlineStr">
+      <c r="E81" s="19" t="inlineStr">
         <is>
           <t>eaa/cli.py</t>
         </is>
       </c>
-      <c r="F77" s="20" t="inlineStr">
+      <c r="F81" s="19" t="inlineStr">
         <is>
           <t>TC-42e</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="20" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="20" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="19" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C78" s="20" t="inlineStr">
+      <c r="C82" s="19" t="inlineStr">
         <is>
           <t>Đọc telemetry UART thật</t>
         </is>
       </c>
-      <c r="D78" s="20" t="inlineStr">
+      <c r="D82" s="19" t="inlineStr">
         <is>
           <t>eaa telemetry thu thẳng từ cổng; diagnose run --port dùng luôn kênh máy sống</t>
         </is>
       </c>
-      <c r="E78" s="20" t="inlineStr">
+      <c r="E82" s="19" t="inlineStr">
         <is>
           <t>eaa/telemetry.py</t>
         </is>
       </c>
-      <c r="F78" s="20" t="inlineStr">
+      <c r="F82" s="19" t="inlineStr">
         <is>
           <t>TC-43 (28 test)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="20" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="20" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="19" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C79" s="20" t="inlineStr">
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>Khung telemetry có checksum</t>
         </is>
       </c>
-      <c r="D79" s="20" t="inlineStr">
+      <c r="D83" s="19" t="inlineStr">
         <is>
           <t>Định dạng khung do dự án khai; mỗi loại hỏng có lý do riêng</t>
         </is>
       </c>
-      <c r="E79" s="20" t="inlineStr">
+      <c r="E83" s="19" t="inlineStr">
         <is>
           <t>eaa/telemetry.py</t>
         </is>
       </c>
-      <c r="F79" s="20" t="inlineStr">
+      <c r="F83" s="19" t="inlineStr">
         <is>
           <t>TC-43a</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="20" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="20" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="19" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C80" s="20" t="inlineStr">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>Phiên thu nhiều khung hỏng bị từ chối</t>
         </is>
       </c>
-      <c r="D80" s="20" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
         <is>
           <t>Vượt ngưỡng thì không kết luận: dữ liệu nhiễu vẫn cho ra số trông hợp lý</t>
         </is>
       </c>
-      <c r="E80" s="20" t="inlineStr">
+      <c r="E84" s="19" t="inlineStr">
         <is>
           <t>eaa/telemetry.py</t>
         </is>
       </c>
-      <c r="F80" s="20" t="inlineStr">
+      <c r="F84" s="19" t="inlineStr">
         <is>
           <t>TC-43c</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="20" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="19" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C81" s="20" t="inlineStr">
+      <c r="C85" s="19" t="inlineStr">
         <is>
           <t>Giữ nguyên văn bản thu, phát lại được</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D85" s="19" t="inlineStr">
         <is>
           <t>Bản thô cạnh bản đã lọc; phân tích lại không cần mạch</t>
         </is>
       </c>
-      <c r="E81" s="20" t="inlineStr">
+      <c r="E85" s="19" t="inlineStr">
         <is>
           <t>eaa telemetry --replay</t>
         </is>
       </c>
-      <c r="F81" s="20" t="inlineStr">
+      <c r="F85" s="19" t="inlineStr">
         <is>
           <t>TC-43d</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="20" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="20" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="19" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C82" s="20" t="inlineStr">
+      <c r="C86" s="19" t="inlineStr">
         <is>
           <t>Sinh firmware chẩn đoán từ mẫu</t>
         </is>
       </c>
-      <c r="D82" s="20" t="inlineStr">
+      <c r="D86" s="19" t="inlineStr">
         <is>
           <t>Bộ khung ở pack + phần đo ở dự án, ghép bằng liên kết; eaa diagnose build</t>
         </is>
       </c>
-      <c r="E82" s="20" t="inlineStr">
+      <c r="E86" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py</t>
         </is>
       </c>
-      <c r="F82" s="20" t="inlineStr">
+      <c r="F86" s="19" t="inlineStr">
         <is>
           <t>TC-44, TC-58a</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="20" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="20" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="19" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C83" s="20" t="inlineStr">
+      <c r="C87" s="19" t="inlineStr">
         <is>
           <t>Không dựng firmware chẩn đoán rỗng</t>
         </is>
       </c>
-      <c r="D83" s="20" t="inlineStr">
+      <c r="D87" s="19" t="inlineStr">
         <is>
           <t>Kịch bản chưa khai phần đo thì dừng — ảnh im lặng không phân biệt được với mạch hỏng</t>
         </is>
       </c>
-      <c r="E83" s="20" t="inlineStr">
+      <c r="E87" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py</t>
         </is>
       </c>
-      <c r="F83" s="20" t="inlineStr">
+      <c r="F87" s="19" t="inlineStr">
         <is>
           <t>TC-44b</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="20" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="20" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C84" s="20" t="inlineStr">
+      <c r="C88" s="19" t="inlineStr">
         <is>
           <t>Checklist an toàn theo ảnh tới lúc nạp</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D88" s="19" t="inlineStr">
         <is>
           <t>Thẻ .meta.json đi kèm ảnh; eaa flash đưa checklist ra đúng lúc người bấm đồng ý</t>
         </is>
       </c>
-      <c r="E84" s="20" t="inlineStr">
+      <c r="E88" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py + eaa/cli.py</t>
         </is>
       </c>
-      <c r="F84" s="20" t="inlineStr">
+      <c r="F88" s="19" t="inlineStr">
         <is>
           <t>TC-44d</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="20" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="20" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="19" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C85" s="20" t="inlineStr">
+      <c r="C89" s="19" t="inlineStr">
         <is>
           <t>Chốt vòng: số đo thật → G4 → phong hạng</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D89" s="19" t="inlineStr">
         <is>
           <t>eaa tune --port thu telemetry, rút số đo theo tiêu chí đã khai, rồi phong hạng</t>
         </is>
       </c>
-      <c r="E85" s="20" t="inlineStr">
+      <c r="E89" s="19" t="inlineStr">
         <is>
           <t>eaa/acceptance.py</t>
         </is>
       </c>
-      <c r="F85" s="20" t="inlineStr">
+      <c r="F89" s="19" t="inlineStr">
         <is>
           <t>TC-45 (23 test)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="20" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="20" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="19" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C86" s="20" t="inlineStr">
+      <c r="C90" s="19" t="inlineStr">
         <is>
           <t>Không phong hạng cho bản chưa từng chạy trên mạch</t>
         </is>
       </c>
-      <c r="D86" s="20" t="inlineStr">
+      <c r="D90" s="19" t="inlineStr">
         <is>
           <t>Nhật ký nạp nói bản khác đang trên chip thì CHẶN; nhật ký trống thì ghi device_verified=false chứ không cấm</t>
         </is>
       </c>
-      <c r="E86" s="20" t="inlineStr">
+      <c r="E90" s="19" t="inlineStr">
         <is>
           <t>eaa/acceptance.py</t>
         </is>
       </c>
-      <c r="F86" s="20" t="inlineStr">
+      <c r="F90" s="19" t="inlineStr">
         <is>
           <t>TC-45a</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="20" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="20" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C87" s="20" t="inlineStr">
+      <c r="C91" s="19" t="inlineStr">
         <is>
           <t>Tiêu chí nghiệm thu có TRƯỚC số đo</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
+      <c r="D91" s="19" t="inlineStr">
         <is>
           <t>acceptance.measurements khai trước; thiếu số đo hay vượt ngưỡng đều chặn phong hạng</t>
         </is>
       </c>
-      <c r="E87" s="20" t="inlineStr">
+      <c r="E91" s="19" t="inlineStr">
         <is>
           <t>constraints.yaml + eaa/acceptance.py</t>
         </is>
       </c>
-      <c r="F87" s="20" t="inlineStr">
+      <c r="F91" s="19" t="inlineStr">
         <is>
           <t>TC-45b, TC-45c, TC-45d</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="20" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="20" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="19" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C88" s="20" t="inlineStr">
+      <c r="C92" s="19" t="inlineStr">
         <is>
           <t>Kiểm sau khi nạp: đọc ngược bộ nhớ</t>
         </is>
       </c>
-      <c r="D88" s="20" t="inlineStr">
+      <c r="D92" s="19" t="inlineStr">
         <is>
           <t>Ba kết cục — khớp / lệch (lần nạp bị coi là trượt) / không kiểm được; 'nạp không báo lỗi' KHÔNG được đọc thành 'nạp đúng'</t>
         </is>
       </c>
-      <c r="E88" s="20" t="inlineStr">
+      <c r="E92" s="19" t="inlineStr">
         <is>
           <t>eaa/flash.py + năng lực flash_verify</t>
         </is>
       </c>
-      <c r="F88" s="20" t="inlineStr">
+      <c r="F92" s="19" t="inlineStr">
         <is>
           <t>TC-52 (12 test)</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="20" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="20" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="19" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C89" s="20" t="inlineStr">
+      <c r="C93" s="19" t="inlineStr">
         <is>
           <t>Đo tay bằng dụng cụ — kênh thứ ba</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
+      <c r="D93" s="19" t="inlineStr">
         <is>
           <t>Dòng tổng, sụt áp trên dây, nhiệt độ vỏ: hướng dẫn đích danh đo cái gì, ở đâu, điều kiện nào, chờ đợi bao nhiêu</t>
         </is>
       </c>
-      <c r="E89" s="20" t="inlineStr">
+      <c r="E93" s="19" t="inlineStr">
         <is>
           <t>eaa/diagnostics.py ManualMeasurement</t>
         </is>
       </c>
-      <c r="F89" s="20" t="inlineStr">
+      <c r="F93" s="19" t="inlineStr">
         <is>
           <t>TC-58c, TC-58d</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="20" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="20" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="19" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C90" s="20" t="inlineStr">
+      <c r="C94" s="19" t="inlineStr">
         <is>
           <t>Đo đặc tính thời gian thực, kể cả xấu nhất</t>
         </is>
       </c>
-      <c r="D90" s="20" t="inlineStr">
+      <c r="D94" s="19" t="inlineStr">
         <is>
           <t>Chu kỳ trung bình, chu kỳ DÀI NHẤT, dao động, tải CPU — ràng buộc áp lên trường hợp xấu nhất chứ không lên trung bình</t>
         </is>
       </c>
-      <c r="E90" s="20" t="inlineStr">
+      <c r="E94" s="19" t="inlineStr">
         <is>
           <t>projects/*/diagnostics/DS-06.c</t>
         </is>
       </c>
-      <c r="F90" s="20" t="inlineStr">
+      <c r="F94" s="19" t="inlineStr">
         <is>
           <t>TC-58b</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="20" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="20" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="19" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C91" s="20" t="inlineStr">
+      <c r="C95" s="19" t="inlineStr">
         <is>
           <t>Kiểm độ bền dài hạn</t>
         </is>
       </c>
-      <c r="D91" s="20" t="inlineStr">
+      <c r="D95" s="19" t="inlineStr">
         <is>
           <t>Phát hiện reset qua bộ đếm thời gian chạy tụt; báo cáo không suy rộng quá quãng đã quan sát</t>
         </is>
       </c>
-      <c r="E91" s="20" t="inlineStr">
+      <c r="E95" s="19" t="inlineStr">
         <is>
           <t>eaa/endurance.py + eaa endurance</t>
         </is>
       </c>
-      <c r="F91" s="20" t="inlineStr">
+      <c r="F95" s="19" t="inlineStr">
         <is>
           <t>TC-58e..g</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="20" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="20" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="19" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>J. Mạch thật &amp; chẩn đoán</t>
         </is>
       </c>
-      <c r="C92" s="20" t="inlineStr">
+      <c r="C96" s="19" t="inlineStr">
         <is>
           <t>Chẩn đoán sự cố ngoài hiện trường</t>
         </is>
       </c>
-      <c r="D92" s="20" t="inlineStr">
+      <c r="D96" s="19" t="inlineStr">
         <is>
           <t>Dựng lại điều kiện trước khi đo; không tái hiện được thì nói CHƯA KẾT LUẬN ĐƯỢC thay vì đoán</t>
         </is>
       </c>
-      <c r="E92" s="20" t="inlineStr">
+      <c r="E96" s="19" t="inlineStr">
         <is>
           <t>eaa/diagnostics.py FieldCase</t>
         </is>
       </c>
-      <c r="F92" s="20" t="inlineStr">
+      <c r="F96" s="19" t="inlineStr">
         <is>
           <t>TC-59e, TC-59f</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="20" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="20" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="19" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>A. Khởi tạo &amp; phạm vi</t>
         </is>
       </c>
-      <c r="C93" s="20" t="inlineStr">
+      <c r="C97" s="19" t="inlineStr">
         <is>
           <t>Agent đề xuất phạm vi, ràng buộc, tiêu chí, bảng chân</t>
         </is>
       </c>
-      <c r="D93" s="20" t="inlineStr">
+      <c r="D97" s="19" t="inlineStr">
         <is>
           <t>Bốn bản đề xuất của G0/G1; mỗi ràng buộc kèm HỆ QUẢ, mỗi tiêu chí là số + đơn vị + cách đo, mỗi chân được kiểm chức năng thay thế</t>
         </is>
       </c>
-      <c r="E93" s="20" t="inlineStr">
+      <c r="E97" s="19" t="inlineStr">
         <is>
           <t>eaa/propose.py</t>
         </is>
       </c>
-      <c r="F93" s="20" t="inlineStr">
+      <c r="F97" s="19" t="inlineStr">
         <is>
           <t>TC-54 (38 test)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="20" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="20" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="19" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>A. Khởi tạo &amp; phạm vi</t>
         </is>
       </c>
-      <c r="C94" s="20" t="inlineStr">
+      <c r="C98" s="19" t="inlineStr">
         <is>
           <t>Danh sách tài liệu và trang cần trích, đích danh</t>
         </is>
       </c>
-      <c r="D94" s="20" t="inlineStr">
+      <c r="D98" s="19" t="inlineStr">
         <is>
           <t>Suy từ hồ sơ phần cứng và đồ thị; chỉ xin phần CÒN THIẾU trích đoạn</t>
         </is>
       </c>
-      <c r="E94" s="20" t="inlineStr">
+      <c r="E98" s="19" t="inlineStr">
         <is>
           <t>eaa/docplan.py</t>
         </is>
       </c>
-      <c r="F94" s="20" t="inlineStr">
+      <c r="F98" s="19" t="inlineStr">
         <is>
           <t>TC-55a..e</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="20" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="20" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="19" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
         <is>
           <t>A. Khởi tạo &amp; phạm vi</t>
         </is>
       </c>
-      <c r="C95" s="20" t="inlineStr">
+      <c r="C99" s="19" t="inlineStr">
         <is>
           <t>Errata theo đúng rev silicon</t>
         </is>
       </c>
-      <c r="D95" s="20" t="inlineStr">
+      <c r="D99" s="19" t="inlineStr">
         <is>
           <t>'Chưa tra' khác hẳn 'chip sạch'; module chạm lỗi đã công bố được gọi tên</t>
         </is>
       </c>
-      <c r="E95" s="20" t="inlineStr">
+      <c r="E99" s="19" t="inlineStr">
         <is>
           <t>eaa/docplan.py ErrataAnalysis</t>
         </is>
       </c>
-      <c r="F95" s="20" t="inlineStr">
+      <c r="F99" s="19" t="inlineStr">
         <is>
           <t>TC-55f..h</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="20" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="20" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="19" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C96" s="20" t="inlineStr">
+      <c r="C100" s="19" t="inlineStr">
         <is>
           <t>Bộ chuẩn đánh giá truy xuất (golden set)</t>
         </is>
       </c>
-      <c r="D96" s="20" t="inlineStr">
+      <c r="D100" s="19" t="inlineStr">
         <is>
           <t>precision@3 trên bộ chuẩn của dự án, kèm chunk nhiễu có chủ ý</t>
         </is>
       </c>
-      <c r="E96" s="20" t="inlineStr">
+      <c r="E100" s="19" t="inlineStr">
         <is>
           <t>eaa/goldenset.py + eaa report retrieval</t>
         </is>
       </c>
-      <c r="F96" s="20" t="inlineStr">
+      <c r="F100" s="19" t="inlineStr">
         <is>
           <t>TC-20 (10 test)</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="20" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="20" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t>C. Tri thức &amp; RAG</t>
         </is>
       </c>
-      <c r="C97" s="20" t="inlineStr">
+      <c r="C101" s="19" t="inlineStr">
         <is>
           <t>Ảnh màn hiện sóng thành số đo đề xuất</t>
         </is>
       </c>
-      <c r="D97" s="20" t="inlineStr">
+      <c r="D101" s="19" t="inlineStr">
         <is>
           <t>Kèm sai số đọc ảnh; người sửa được giá trị trước khi lưu, bản ghi giữ cả hai số</t>
         </is>
       </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="E101" s="19" t="inlineStr">
         <is>
           <t>eaa/ingest.py ScopeImageReader</t>
         </is>
       </c>
-      <c r="F97" s="20" t="inlineStr">
+      <c r="F101" s="19" t="inlineStr">
         <is>
           <t>TC-23 (10 test)</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="20" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="20" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="19" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C98" s="20" t="inlineStr">
+      <c r="C102" s="19" t="inlineStr">
         <is>
           <t>Sinh giao diện TRƯỚC khi sinh thân</t>
         </is>
       </c>
-      <c r="D98" s="20" t="inlineStr">
+      <c r="D102" s="19" t="inlineStr">
         <is>
           <t>Hợp đồng gọi trả lời ba câu chữ ký không nói được: ngắt / chặn / tái nhập</t>
         </is>
       </c>
-      <c r="E98" s="20" t="inlineStr">
+      <c r="E102" s="19" t="inlineStr">
         <is>
           <t>eaa/interfaces.py + khuôn của pack</t>
         </is>
       </c>
-      <c r="F98" s="20" t="inlineStr">
+      <c r="F102" s="19" t="inlineStr">
         <is>
           <t>TC-56a..e</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="20" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="20" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="19" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
         <is>
           <t>D. Sinh mã</t>
         </is>
       </c>
-      <c r="C99" s="20" t="inlineStr">
+      <c r="C103" s="19" t="inlineStr">
         <is>
           <t>Ngân sách tài nguyên và token chia theo module</t>
         </is>
       </c>
-      <c r="D99" s="20" t="inlineStr">
+      <c r="D103" s="19" t="inlineStr">
         <is>
           <t>Cảnh báo khi một module ăn quá phần; trần token tích lũy chặn TRƯỚC khi gọi mô hình</t>
         </is>
       </c>
-      <c r="E99" s="20" t="inlineStr">
+      <c r="E103" s="19" t="inlineStr">
         <is>
           <t>eaa/budget.py + eaa budget</t>
         </is>
       </c>
-      <c r="F99" s="20" t="inlineStr">
+      <c r="F103" s="19" t="inlineStr">
         <is>
           <t>TC-53 (30 test)</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="20" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="20" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="19" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C100" s="20" t="inlineStr">
+      <c r="C104" s="19" t="inlineStr">
         <is>
           <t>Nêu đích danh phần KHÔNG kiểm được trên máy chủ</t>
         </is>
       </c>
-      <c r="D100" s="20" t="inlineStr">
+      <c r="D104" s="19" t="inlineStr">
         <is>
           <t>Thanh ghi, ngoại vi, ràng buộc thời gian — mỗi loại chỉ ra nơi nó được đóng</t>
         </is>
       </c>
-      <c r="E100" s="20" t="inlineStr">
+      <c r="E104" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/unittests.py host_gaps</t>
         </is>
       </c>
-      <c r="F100" s="20" t="inlineStr">
+      <c r="F104" s="19" t="inlineStr">
         <is>
           <t>TC-56f, TC-56g</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="20" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="20" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="19" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>E. Kiểm chứng &amp; cổng</t>
         </is>
       </c>
-      <c r="C101" s="20" t="inlineStr">
+      <c r="C105" s="19" t="inlineStr">
         <is>
           <t>Khoảng trống ngăn xếp ở tầm firmware</t>
         </is>
       </c>
-      <c r="D101" s="20" t="inlineStr">
+      <c r="D105" s="19" t="inlineStr">
         <is>
           <t>Số liệu SUY RA từ dung lượng trừ phần đã dùng; chỉ có nghĩa sau khi liên kết</t>
         </is>
       </c>
-      <c r="E101" s="20" t="inlineStr">
+      <c r="E105" s="19" t="inlineStr">
         <is>
           <t>eaa/budget.py derived</t>
         </is>
       </c>
-      <c r="F101" s="20" t="inlineStr">
+      <c r="F105" s="19" t="inlineStr">
         <is>
           <t>TC-53d</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="20" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="20" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="19" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>F. Mô phỏng</t>
         </is>
       </c>
-      <c r="C102" s="20" t="inlineStr">
+      <c r="C106" s="19" t="inlineStr">
         <is>
           <t>Tiêm lỗi trong mô phỏng</t>
         </is>
       </c>
-      <c r="D102" s="20" t="inlineStr">
+      <c r="D106" s="19" t="inlineStr">
         <is>
           <t>Bốn kiểu hỏng đặt tên theo hành vi; kiểm hệ có vào chế độ an toàn không</t>
         </is>
       </c>
-      <c r="E102" s="20" t="inlineStr">
+      <c r="E106" s="19" t="inlineStr">
         <is>
           <t>eaa/tools/sim_runner.py FaultSpec</t>
         </is>
       </c>
-      <c r="F102" s="20" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr">
         <is>
           <t>TC-57a..e</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="20" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="20" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="19" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>F. Mô phỏng</t>
         </is>
       </c>
-      <c r="C103" s="20" t="inlineStr">
+      <c r="C107" s="19" t="inlineStr">
         <is>
           <t>Đề xuất mô hình đối tượng</t>
         </is>
       </c>
-      <c r="D103" s="20" t="inlineStr">
+      <c r="D107" s="19" t="inlineStr">
         <is>
           <t>Tham số chưa đo vào Assumption Log; mô hình BẮT BUỘC nêu hiện tượng nó bỏ qua</t>
         </is>
       </c>
-      <c r="E103" s="20" t="inlineStr">
+      <c r="E107" s="19" t="inlineStr">
         <is>
           <t>eaa/propose.py PlantModelProposal</t>
         </is>
       </c>
-      <c r="F103" s="20" t="inlineStr">
+      <c r="F107" s="19" t="inlineStr">
         <is>
           <t>TC-57f, TC-57g</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="20" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="20" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="19" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>K. Bàn giao &amp; vận hành</t>
         </is>
       </c>
-      <c r="C104" s="20" t="inlineStr">
+      <c r="C108" s="19" t="inlineStr">
         <is>
           <t>Tài liệu vận hành sinh từ dữ liệu dự án</t>
         </is>
       </c>
-      <c r="D104" s="20" t="inlineStr">
+      <c r="D108" s="19" t="inlineStr">
         <is>
           <t>Kèm mục 'điều hệ thống KHÔNG làm được', dựng từ chỗ hở thật chứ không viết tay</t>
         </is>
       </c>
-      <c r="E104" s="20" t="inlineStr">
+      <c r="E108" s="19" t="inlineStr">
         <is>
           <t>eaa/handover.py + eaa handover doc</t>
         </is>
       </c>
-      <c r="F104" s="20" t="inlineStr">
+      <c r="F108" s="19" t="inlineStr">
         <is>
           <t>TC-59a, TC-59b</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="20" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="20" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="19" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>K. Bàn giao &amp; vận hành</t>
         </is>
       </c>
-      <c r="C105" s="20" t="inlineStr">
+      <c r="C109" s="19" t="inlineStr">
         <is>
           <t>Đánh giá ảnh hưởng khi đổi linh kiện</t>
         </is>
       </c>
-      <c r="D105" s="20" t="inlineStr">
+      <c r="D109" s="19" t="inlineStr">
         <is>
           <t>So hai linh kiện rồi bắc cầu trên đồ thị ra module bị chạm</t>
         </is>
       </c>
-      <c r="E105" s="20" t="inlineStr">
+      <c r="E109" s="19" t="inlineStr">
         <is>
           <t>eaa/handover.py SwapAnalysis</t>
         </is>
       </c>
-      <c r="F105" s="20" t="inlineStr">
+      <c r="F109" s="19" t="inlineStr">
         <is>
           <t>TC-59c, TC-59d</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="20" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="20" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>K. Bàn giao &amp; vận hành</t>
         </is>
       </c>
-      <c r="C106" s="20" t="inlineStr">
+      <c r="C110" s="19" t="inlineStr">
         <is>
           <t>Cập nhật thiết bị đã triển khai</t>
         </is>
       </c>
-      <c r="D106" s="20" t="inlineStr">
+      <c r="D110" s="19" t="inlineStr">
         <is>
           <t>Bậc đầu ĐÚNG MỘT thiết bị; phải có đường lui lấy từ known_good.lock</t>
         </is>
       </c>
-      <c r="E106" s="20" t="inlineStr">
+      <c r="E110" s="19" t="inlineStr">
         <is>
           <t>eaa/handover.py RolloutPlan</t>
         </is>
       </c>
-      <c r="F106" s="20" t="inlineStr">
+      <c r="F110" s="19" t="inlineStr">
         <is>
           <t>TC-59g, TC-59h</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="20" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="20" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="19" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>L. Siêu nghiệp vụ</t>
         </is>
       </c>
-      <c r="C107" s="20" t="inlineStr">
+      <c r="C111" s="19" t="inlineStr">
+        <is>
+          <t>Bộ từ vựng mức tin cậy dùng chung</t>
+        </is>
+      </c>
+      <c r="D111" s="19" t="inlineStr">
+        <is>
+          <t>ĐÃ KIỂM / SUY RA / GIẢ ĐỊNH / KHÔNG KIỂM ĐƯỢC — 23 lớp kết luận cùng dùng</t>
+        </is>
+      </c>
+      <c r="E111" s="19" t="inlineStr">
+        <is>
+          <t>eaa/confidence.py</t>
+        </is>
+      </c>
+      <c r="F111" s="19" t="inlineStr">
+        <is>
+          <t>TC-60a..c, TC-63a..e</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="19" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="19" t="inlineStr">
+        <is>
+          <t>L. Siêu nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C112" s="19" t="inlineStr">
+        <is>
+          <t>Test canh ĐỘ PHỦ của nhãn tin cậy</t>
+        </is>
+      </c>
+      <c r="D112" s="19" t="inlineStr">
+        <is>
+          <t>Thêm lớp sinh kết luận mà quên gắn nhãn thì bộ test đỏ ngay</t>
+        </is>
+      </c>
+      <c r="E112" s="19" t="inlineStr">
+        <is>
+          <t>tests/test_tc63_confidence_coverage.py</t>
+        </is>
+      </c>
+      <c r="F112" s="19" t="inlineStr">
+        <is>
+          <t>TC-63a</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="19" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="19" t="inlineStr">
+        <is>
+          <t>L. Siêu nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C113" s="19" t="inlineStr">
         <is>
           <t>Agent tự phát hiện sai lệch thiết kế</t>
         </is>
       </c>
-      <c r="D107" s="20" t="inlineStr">
+      <c r="D113" s="19" t="inlineStr">
         <is>
           <t>Đối chiếu module và lệnh với tài liệu; dựng nháp mục cho sổ sai lệch</t>
         </is>
       </c>
-      <c r="E107" s="20" t="inlineStr">
+      <c r="E113" s="19" t="inlineStr">
         <is>
           <t>eaa/deviation.py + eaa deviations</t>
         </is>
       </c>
-      <c r="F107" s="20" t="inlineStr">
+      <c r="F113" s="19" t="inlineStr">
         <is>
           <t>TC-60d..f</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="20" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="20" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="19" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="19" t="inlineStr">
         <is>
           <t>L. Siêu nghiệp vụ</t>
         </is>
       </c>
-      <c r="C108" s="20" t="inlineStr">
+      <c r="C114" s="19" t="inlineStr">
         <is>
           <t>Tự đánh giá quy trình</t>
         </is>
       </c>
-      <c r="D108" s="20" t="inlineStr">
+      <c r="D114" s="19" t="inlineStr">
         <is>
           <t>Chỉ ra cổng hay trượt nhất; mỗi đề xuất gắn với một con số quan sát được</t>
         </is>
       </c>
-      <c r="E108" s="20" t="inlineStr">
+      <c r="E114" s="19" t="inlineStr">
         <is>
           <t>eaa/kpi.py weak_points + eaa report review</t>
         </is>
       </c>
-      <c r="F108" s="20" t="inlineStr">
+      <c r="F114" s="19" t="inlineStr">
         <is>
           <t>TC-60g..i</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F108"/>
+  <autoFilter ref="A1:F114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4387,7 +4561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4431,187 +4605,97 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>L. Siêu nghiệp vụ</t>
-        </is>
-      </c>
-      <c r="C2" s="20" t="inlineStr">
-        <is>
-          <t>Bộ từ vựng mức tin cậy dùng chung</t>
-        </is>
-      </c>
-      <c r="D2" s="20" t="inlineStr">
-        <is>
-          <t>ĐÃ KIỂM / SUY RA / GIẢ ĐỊNH / KHÔNG KIỂM ĐƯỢC — một bộ cho toàn hệ</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>Một phần</t>
-        </is>
-      </c>
-      <c r="F2" s="20" t="inlineStr">
-        <is>
-          <t>Năm chỗ đã quy về bộ từ vựng chung; các đầu ra còn lại chưa gắn nhãn</t>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>E. Kiểm chứng &amp; cổng</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>Cổng SIL cho mã C sinh ra</t>
+        </is>
+      </c>
+      <c r="D2" s="19" t="inlineStr">
+        <is>
+          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
+        </is>
+      </c>
+      <c r="E2" s="20" t="inlineStr">
+        <is>
+          <t>Chưa làm</t>
+        </is>
+      </c>
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="n">
+      <c r="A3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="inlineStr">
-        <is>
-          <t>C. Tri thức &amp; RAG</t>
-        </is>
-      </c>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>BM25 bổ trợ truy xuất theo từ khóa</t>
-        </is>
-      </c>
-      <c r="D3" s="20" t="inlineStr">
-        <is>
-          <t>Tầng 2 của AIS §4.2</t>
-        </is>
-      </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>J. Mạch thật &amp; chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Chưa làm</t>
         </is>
       </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>Đã hoãn có chủ ý: đồ thị + khớp tên thanh ghi đang đủ cho phạm vi MVP</t>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>E. Kiểm chứng &amp; cổng</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>Cổng SIL cho mã C sinh ra</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>Chạy chính mã C sinh ra trong mô phỏng, không chỉ mô hình Python</t>
-        </is>
-      </c>
-      <c r="E4" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>Cố ý để ngoài chuỗi tự động: nếu nối vào mà không thật sự chạy artifact thì cổng sẽ 'đạt' mà chẳng kiểm gì — nguy hiểm hơn là không có cổng</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>I. Tương tác</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>Giao diện hội thoại / TUI</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>Hiện là CLI từng lệnh rời</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>Không chặn gì về kỹ thuật; là tiện dụng, nên xếp sau các mắt xích mạch thật</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>J. Mạch thật &amp; chẩn đoán</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>Debug sâu qua debugWIRE / JTAG / SWD</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>Đặt điểm dừng, đọc thanh ghi lúc chạy</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>Chưa làm</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>Ngoài phạm vi đề án; UART + nạp lại là đủ cho vòng chẩn đoán hai kênh</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>G. Công cụ &amp; môi trường</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>Tự cài KHÔNG hỏi người</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>Kỹ thuật làm được trong một buổi, nhưng FR-ENV-02 và AIS §9.4 cấm</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>Cố ý không làm</t>
         </is>
       </c>
-      <c r="F7" s="20" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Cài phần mềm là thay đổi máy kỹ sư. Một agent tự cài im lặng là một agent có quyền ghi tùy ý lên máy — bỏ chốt này thì hai chốt còn lại mất ý nghĩa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7"/>
+  <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4633,7 +4717,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Lộ trình nối Agent với mạch thật qua USB</t>
         </is>
@@ -4674,216 +4758,216 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>1 ✔</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Tách biên dịch và liên kết — XONG</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>compile dùng -c cho từng tệp nguồn; link gộp tệp đối tượng + main() thành .elf; hex đổi sang định dạng nạp được. TC-40, 19 test</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Chưa có bước này thì KHÔNG CÓ TỆP ĐỂ NẠP — mọi bước sau vô nghĩa</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>packs/avr/pack.yaml, eaa/tools/compile.py, eaa/platform.py</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>2 ✔</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Ráp firmware hoàn chỉnh — XONG</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Khuôn vòng lặp chính ở pack (bộ định thời hợp tác); firmware.yaml khai module nào chạy mỗi bao nhiêu ms; `eaa build` dịch, liên kết, ra .hex. TC-41</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Biến các module rời thành một chương trình chạy được trên chip</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>packs/avr/templates/, eaa/firmware.py, eaa/cli.py</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>3 ✔</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Liệt kê cổng USB — XONG</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>eaa ports; khớp VID/PID với bo khai ở hardware_profile.yaml; thiếu pyserial thì nói thẳng là không đọc được VID/PID. TC-42a</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Agent trả lời được 'bạn đang cắm mạch nào vào cổng nào'</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>eaa/serialport.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>4 ✔</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Lệnh nạp firmware — XONG</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>eaa flash: bốn phép kiểm (có ảnh · kho sạch · ảnh mới hơn nguồn · người xác nhận) rồi mới nạp; nhật ký append-only ghi cả lần trượt. TC-42</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Đây là lần đầu Agent chạm vào phần cứng thật</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>eaa/flash.py, eaa/cli.py</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>5 ✔</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Bộ đọc telemetry UART — XONG</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>eaa telemetry: hạn thời gian bắt buộc, khung hỏng được đếm, bản nguyên văn giữ lại và phát lại được; diagnose run --port từ chối kết luận trên phiên không tin được. TC-43</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Kênh máy của chẩn đoán hai kênh chuyển từ 'đọc tệp' sang 'đọc mạch'</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>eaa/telemetry.py, eaa/cli.py</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="23" t="inlineStr">
         <is>
           <t>6 ✔</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Sinh firmware chẩn đoán — XONG (2/6 kịch bản)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>eaa diagnose build: bộ khung của pack + phần đo của dự án, ghép bằng liên kết. Ảnh mang thẻ an toàn tới tận lúc nạp. TC-44</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>Mỗi kịch bản chẩn đoán tự chạy được thay vì cần người viết mã đo</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>eaa/firmware.py, packs/avr/templates/, projects/*/diagnostics/</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>7 ✔</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Khép vòng số đo → G4 — XONG</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>eaa tune --port: thu telemetry → rút số đo theo tiêu chí đã khai → G4 → hw-verified. Commit phong hạng phải là commit đang chạy trên thiết bị. TC-45</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Vòng đời ba hạng chất lượng khép kín, không còn nhập tay</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>eaa/acceptance.py, eaa/cli.py</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>8 ✔</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Gate nhiều phương án — XONG</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>eaa decide dựng N phương án kèm đánh đổi; approve ĐÒI --option và không lấy gợi ý làm mặc định; cả tập (kể cả cái bị loại) vào quyết định. TC-46</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Đúng điều bạn nêu: 'tương tác với người dùng chọn giải pháp phù hợp'</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>eaa/options.py, eaa/gates.py, eaa/cli.py</t>
         </is>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -580,7 +580,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-08-30</t>
+          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -580,7 +580,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-08-31</t>
+          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-09-04</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gemini-3.1-pro-preview (ghim phiên bản)</t>
+          <t>gemini-3.8-flash (ghim phiên bản, mặc định từ 04/09/2026)</t>
         </is>
       </c>
     </row>

--- a/docs/EAA_Thong_ke_tinh_nang.xlsx
+++ b/docs/EAA_Thong_ke_tinh_nang.xlsx
@@ -580,7 +580,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-09-04</t>
+          <t>Đề án Thạc sĩ Kỹ thuật (Kỹ thuật Điện tử, PTIT) · Học viên: Vũ Trí Công · Giảng viên hướng dẫn: TS. Nguyễn Trung Hiếu · cập nhật 2026-09-05</t>
         </is>
       </c>
     </row>
